--- a/figs/exps/performance.xlsx
+++ b/figs/exps/performance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\GitHub\VideoMMEv2\figs\exps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC3DB006-8E60-4AC3-BF2D-0BBC11290993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516D56E3-7C7D-4CD3-BDE6-ADE56BFDACF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="133">
   <si>
     <t>模型</t>
   </si>
@@ -838,9 +838,6 @@
     <t>在推</t>
   </si>
   <si>
-    <t>H201</t>
-  </si>
-  <si>
     <t>Qwen2_5-VL-72B-Instruct-sub</t>
   </si>
   <si>
@@ -1243,9 +1240,6 @@
     <t>InternVL3_5-241B-A28B-Instruct-sub</t>
   </si>
   <si>
-    <t>H20_qwen25_vl</t>
-  </si>
-  <si>
     <t>KimiVL-16B-A3B-Instruct</t>
   </si>
   <si>
@@ -1266,9 +1260,6 @@
 top_k: 20
 top_p: 0.95
 max_tokens: 2024</t>
-  </si>
-  <si>
-    <t>vllm</t>
   </si>
   <si>
     <t>MiMo-VL-7B-SFT-2508-sub</t>
@@ -1656,9 +1647,6 @@
 }</t>
   </si>
   <si>
-    <t>H20_3&amp;H20_5x4</t>
-  </si>
-  <si>
     <t>Qwen3vl-30B-A3B-Think-sub</t>
   </si>
   <si>
@@ -1926,9 +1914,6 @@
 max_tokens: 32768</t>
   </si>
   <si>
-    <t>H20_4</t>
-  </si>
-  <si>
     <t>KimiVL-16B-A3B-Think-sub</t>
   </si>
   <si>
@@ -1982,6 +1967,1149 @@
   </si>
   <si>
     <t>GLM4.6-flash-sub</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 17.28858784893268,
+"level_2": 13.04,
+"level_3": 12.862787356321839,
+"relevance_score": 14.808238636363637,
+"relevance_linear_score": 28.645833333333332,
+"logic_score": 12.553418803418804,
+"total": 14.039741989180191
+},
+"second_head_rating": {
+"Physical World Reasoning": 9.755892255892256,
+"Video-Based Knowledge Acquisition": 14.257662835249043,
+"Complex Plot Comprehension": 16.379310344827587,
+"Temporal Reasoning": 10.93939393939394,
+"Order": 17.027777777777775,
+"Change": 15.985576923076923,
+"Social Behavior Analysis": 11.266666666666667,
+"Action &amp; Motion": 8.088235294117647,
+"Frame-Only": 17.80263157894737,
+"Frames &amp; Audio": 16.836419753086417
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 10.0,
+"Counterfactual Reasoning": 8.928571428571429,
+"Professional Knowledge Acquisition": 18.693181818181817,
+"High-Order Narrative Deconstruction": 6.726190476190476,
+"Symbolic/Metaphorical Interpretation": 27.067307692307693,
+"Narrative Turning Point Detection": 19.047619047619047,
+"Causal Reasoning": 10.833333333333334,
+"Event Sequence Ordering": 16.379310344827587,
+"Scene Transformation Detection": 23.4375,
+"Entity Attribute Change Detection": 12.0,
+"Object Appearance Ordering": 18.51851851851852,
+"Individual Social Cognition": 16.333333333333332,
+"Collective Dynamics Analysis": 9.038461538461538,
+"General Skills Acquisition": 9.718992248062015,
+"Spatial Understanding": 8.8,
+"Counterintuitive Comprehension": 11.011904761904761,
+"Fine-Grained Action Recognition": 3.3333333333333335,
+"Visual Recognition": 29.86842105263158,
+"Dyadic Interaction Dynamics": 8.402777777777777,
+"Audio-Guided Visual Description": 9.25,
+"Narrative Cloze Inference": 9.473684210526315,
+"Future Event Prediction": 11.08695652173913,
+"Entity Existence Change Detection": 16.666666666666668,
+"Temporal Periodicity Detection": 15.899122807017543,
+"Repetitive Action Counting": 1.0416666666666667,
+"Temporal Action Localization": 11.25,
+"Motion Trajectory Estimation": 8.75,
+"Basic Counting": 5.769230769230769,
+"Numerical Calculation": 13.10483870967742,
+"Cross-Modal Semantic Consistency": 37.026515151515156,
+"Vision-Guided Audio Description": 11.684782608695652,
+"Visual-Audio Collaborative Reasoning": 13.256578947368421,
+"Motion Properties Analysis": 15.234375
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 26.120689655172413,
+"level_2": 20.37333333333333,
+"level_3": 20.292145593869733,
+"relevance_score": 21.022727272727273,
+"relevance_linear_score": 36.07954545454545,
+"logic_score": 23.28754578754579,
+"total": 21.794631710362047
+},
+"second_head_rating": {
+"Physical World Reasoning": 14.54124579124579,
+"Video-Based Knowledge Acquisition": 23.18007662835249,
+"Complex Plot Comprehension": 22.65325670498084,
+"Temporal Reasoning": 22.113636363636363,
+"Order": 28.944444444444446,
+"Change": 19.951923076923077,
+"Social Behavior Analysis": 21.794444444444444,
+"Action &amp; Motion": 9.834558823529411,
+"Frame-Only": 18.916666666666664,
+"Frames &amp; Audio": 32.45756172839506
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 12.0,
+"Counterfactual Reasoning": 16.666666666666668,
+"Professional Knowledge Acquisition": 23.285984848484848,
+"High-Order Narrative Deconstruction": 12.083333333333334,
+"Symbolic/Metaphorical Interpretation": 25.60897435897436,
+"Narrative Turning Point Detection": 32.04365079365079,
+"Causal Reasoning": 22.356770833333332,
+"Event Sequence Ordering": 36.206896551724135,
+"Scene Transformation Detection": 27.083333333333332,
+"Entity Attribute Change Detection": 19.5,
+"Object Appearance Ordering": 27.314814814814813,
+"Individual Social Cognition": 32.333333333333336,
+"Collective Dynamics Analysis": 19.69551282051282,
+"General Skills Acquisition": 23.07170542635659,
+"Spatial Understanding": 10.9,
+"Counterintuitive Comprehension": 18.467261904761905,
+"Fine-Grained Action Recognition": 6.666666666666667,
+"Visual Recognition": 31.842105263157894,
+"Dyadic Interaction Dynamics": 13.090277777777779,
+"Audio-Guided Visual Description": 16.0,
+"Narrative Cloze Inference": 19.912280701754383,
+"Future Event Prediction": 21.77536231884058,
+"Entity Existence Change Detection": 15.0,
+"Temporal Periodicity Detection": 20.175438596491226,
+"Repetitive Action Counting": 1.5625,
+"Temporal Action Localization": 11.25,
+"Motion Trajectory Estimation": 9.166666666666666,
+"Basic Counting": 6.490384615384615,
+"Numerical Calculation": 13.49462365591398,
+"Cross-Modal Semantic Consistency": 30.492424242424246,
+"Vision-Guided Audio Description": 35.05434782608695,
+"Visual-Audio Collaborative Reasoning": 42.85087719298245,
+"Motion Properties Analysis": 18.75
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 18.3435960591133,
+"level_2": 14.231666666666666,
+"level_3": 14.689894636015325,
+"relevance_score": 16.40625,
+"relevance_linear_score": 31.34469696969697,
+"logic_score": 13.667582417582418,
+"total": 15.472846441947565
+},
+"second_head_rating": {
+"Physical World Reasoning": 9.722222222222221,
+"Video-Based Knowledge Acquisition": 15.21551724137931,
+"Complex Plot Comprehension": 20.61302681992337,
+"Temporal Reasoning": 12.606060606060607,
+"Order": 20.527777777777775,
+"Change": 10.216346153846153,
+"Social Behavior Analysis": 13.766666666666667,
+"Action &amp; Motion": 11.672794117647058,
+"Frame-Only": 19.385964912280702,
+"Frames &amp; Audio": 17.426697530864196
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 12.9,
+"Counterfactual Reasoning": 7.738095238095238,
+"Professional Knowledge Acquisition": 16.410984848484848,
+"High-Order Narrative Deconstruction": 11.19047619047619,
+"Symbolic/Metaphorical Interpretation": 26.73076923076923,
+"Narrative Turning Point Detection": 25.595238095238095,
+"Causal Reasoning": 13.828125,
+"Event Sequence Ordering": 22.629310344827587,
+"Scene Transformation Detection": 16.145833333333332,
+"Entity Attribute Change Detection": 8.5,
+"Object Appearance Ordering": 21.064814814814813,
+"Individual Social Cognition": 20.9,
+"Collective Dynamics Analysis": 8.493589743589745,
+"General Skills Acquisition": 13.992248062015504,
+"Spatial Understanding": 6.8,
+"Counterintuitive Comprehension": 10.982142857142858,
+"Fine-Grained Action Recognition": 8.75,
+"Visual Recognition": 36.348684210526315,
+"Dyadic Interaction Dynamics": 12.048611111111112,
+"Audio-Guided Visual Description": 22.0,
+"Narrative Cloze Inference": 17.149122807017545,
+"Future Event Prediction": 10.905797101449275,
+"Entity Existence Change Detection": 8.333333333333334,
+"Temporal Periodicity Detection": 16.557017543859647,
+"Repetitive Action Counting": 1.5625,
+"Temporal Action Localization": 5.625,
+"Motion Trajectory Estimation": 16.25,
+"Basic Counting": 3.605769230769231,
+"Numerical Calculation": 11.827956989247312,
+"Cross-Modal Semantic Consistency": 33.901515151515156,
+"Vision-Guided Audio Description": 12.5,
+"Visual-Audio Collaborative Reasoning": 7.8618421052631575,
+"Motion Properties Analysis": 21.484375
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 25.660919540229887,
+"level_2": 22.311666666666667,
+"level_3": 19.2397030651341,
+"relevance_score": 21.60274621212121,
+"relevance_linear_score": 37.35795454545455,
+"logic_score": 22.257326007326007,
+"total": 21.825842696629213
+},
+"second_head_rating": {
+"Physical World Reasoning": 12.44949494949495,
+"Video-Based Knowledge Acquisition": 21.671455938697317,
+"Complex Plot Comprehension": 23.620689655172413,
+"Temporal Reasoning": 30.46969696969697,
+"Order": 28.611111111111114,
+"Change": 16.826923076923077,
+"Social Behavior Analysis": 20.3,
+"Action &amp; Motion": 12.959558823529411,
+"Frame-Only": 20.30263157894737,
+"Frames &amp; Audio": 30.374228395061728
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 8.15,
+"Counterfactual Reasoning": 11.011904761904763,
+"Professional Knowledge Acquisition": 19.867424242424242,
+"High-Order Narrative Deconstruction": 14.345238095238095,
+"Symbolic/Metaphorical Interpretation": 26.458333333333332,
+"Narrative Turning Point Detection": 35.416666666666664,
+"Causal Reasoning": 30.15625,
+"Event Sequence Ordering": 43.75,
+"Scene Transformation Detection": 27.083333333333332,
+"Entity Attribute Change Detection": 15.5,
+"Object Appearance Ordering": 22.685185185185187,
+"Individual Social Cognition": 27.083333333333336,
+"Collective Dynamics Analysis": 17.628205128205128,
+"General Skills Acquisition": 23.517441860465116,
+"Spatial Understanding": 6.3,
+"Counterintuitive Comprehension": 22.857142857142858,
+"Fine-Grained Action Recognition": 8.75,
+"Visual Recognition": 38.1578947368421,
+"Dyadic Interaction Dynamics": 16.12847222222222,
+"Audio-Guided Visual Description": 21.5,
+"Narrative Cloze Inference": 16.95175438596491,
+"Future Event Prediction": 30.905797101449277,
+"Entity Existence Change Detection": 10.833333333333334,
+"Temporal Periodicity Detection": 13.925438596491228,
+"Repetitive Action Counting": 3.125,
+"Temporal Action Localization": 13.125,
+"Motion Trajectory Estimation": 13.333333333333334,
+"Basic Counting": 6.490384615384615,
+"Numerical Calculation": 10.0,
+"Cross-Modal Semantic Consistency": 32.765151515151516,
+"Vision-Guided Audio Description": 30.16304347826087,
+"Visual-Audio Collaborative Reasoning": 34.95614035087719,
+"Motion Properties Analysis": 23.828125
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 20.398193760262725,
+"level_2": 12.996666666666666,
+"level_3": 13.603927203065135,
+"relevance_score": 16.50094696969697,
+"relevance_linear_score": 30.96590909090909,
+"logic_score": 12.496947496947497,
+"total": 15.136287973366624
+},
+"second_head_rating": {
+"Physical World Reasoning": 8.484848484848484,
+"Video-Based Knowledge Acquisition": 15.067049808429118,
+"Complex Plot Comprehension": 17.169540229885058,
+"Temporal Reasoning": 14.159090909090908,
+"Order": 13.305555555555555,
+"Change": 14.302884615384615,
+"Social Behavior Analysis": 14.527777777777777,
+"Action &amp; Motion": 10.716911764705882,
+"Frame-Only": 23.039473684210527,
+"Frames &amp; Audio": 18.074845679012345
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 13.0,
+"Counterfactual Reasoning": 6.34920634920635,
+"Professional Knowledge Acquisition": 17.1875,
+"High-Order Narrative Deconstruction": 14.642857142857142,
+"Symbolic/Metaphorical Interpretation": 20.240384615384617,
+"Narrative Turning Point Detection": 19.841269841269842,
+"Causal Reasoning": 17.1484375,
+"Event Sequence Ordering": 15.086206896551724,
+"Scene Transformation Detection": 10.416666666666666,
+"Entity Attribute Change Detection": 16.0,
+"Object Appearance Ordering": 10.416666666666666,
+"Individual Social Cognition": 19.233333333333334,
+"Collective Dynamics Analysis": 10.128205128205128,
+"General Skills Acquisition": 12.897286821705427,
+"Spatial Understanding": 6.9,
+"Counterintuitive Comprehension": 7.470238095238096,
+"Fine-Grained Action Recognition": 4.416666666666667,
+"Visual Recognition": 40.82236842105263,
+"Dyadic Interaction Dynamics": 14.392361111111112,
+"Audio-Guided Visual Description": 20.25,
+"Narrative Cloze Inference": 12.807017543859649,
+"Future Event Prediction": 10.0,
+"Entity Existence Change Detection": 14.583333333333334,
+"Temporal Periodicity Detection": 14.692982456140351,
+"Repetitive Action Counting": 7.8125,
+"Temporal Action Localization": 18.125,
+"Motion Trajectory Estimation": 11.25,
+"Basic Counting": 12.740384615384615,
+"Numerical Calculation": 9.879032258064516,
+"Cross-Modal Semantic Consistency": 37.026515151515156,
+"Vision-Guided Audio Description": 6.25,
+"Visual-Audio Collaborative Reasoning": 12.828947368421053,
+"Motion Properties Analysis": 13.671875
+}
+}</t>
+  </si>
+  <si>
+    <t>a{
+"final_rating": {
+"level_1": 22.76067323481117,
+"level_2": 16.958333333333332,
+"level_3": 18.21000957854406,
+"relevance_score": 19.53125,
+"relevance_linear_score": 35.321969696969695,
+"logic_score": 17.89224664224664,
+"total": 18.972638368705784
+},
+"second_head_rating": {
+"Physical World Reasoning": 10.610269360269362,
+"Video-Based Knowledge Acquisition": 20.407088122605366,
+"Complex Plot Comprehension": 21.671455938697317,
+"Temporal Reasoning": 21.21969696969697,
+"Order": 19.333333333333332,
+"Change": 16.10576923076923,
+"Social Behavior Analysis": 21.677777777777777,
+"Action &amp; Motion": 11.544117647058824,
+"Frame-Only": 21.19736842105263,
+"Frames &amp; Audio": 24.1358024691358
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 17.75,
+"Counterfactual Reasoning": 8.432539682539684,
+"Professional Knowledge Acquisition": 22.452651515151516,
+"High-Order Narrative Deconstruction": 19.285714285714285,
+"Symbolic/Metaphorical Interpretation": 21.939102564102562,
+"Narrative Turning Point Detection": 27.28174603174603,
+"Causal Reasoning": 23.59375,
+"Event Sequence Ordering": 24.78448275862069,
+"Scene Transformation Detection": 7.8125,
+"Entity Attribute Change Detection": 23.25,
+"Object Appearance Ordering": 17.12962962962963,
+"Individual Social Cognition": 29.733333333333334,
+"Collective Dynamics Analysis": 18.01282051282051,
+"General Skills Acquisition": 18.313953488372093,
+"Spatial Understanding": 7.9,
+"Counterintuitive Comprehension": 8.288690476190476,
+"Fine-Grained Action Recognition": 6.083333333333333,
+"Visual Recognition": 39.01315789473684,
+"Dyadic Interaction Dynamics": 17.256944444444446,
+"Audio-Guided Visual Description": 14.25,
+"Narrative Cloze Inference": 17.74122807017544,
+"Future Event Prediction": 17.916666666666664,
+"Entity Existence Change Detection": 10.833333333333334,
+"Temporal Periodicity Detection": 14.144736842105264,
+"Repetitive Action Counting": 4.6875,
+"Temporal Action Localization": 11.25,
+"Motion Trajectory Estimation": 10.416666666666666,
+"Basic Counting": 9.375,
+"Numerical Calculation": 9.274193548387096,
+"Cross-Modal Semantic Consistency": 33.61742424242424,
+"Vision-Guided Audio Description": 16.304347826086957,
+"Visual-Audio Collaborative Reasoning": 29.89035087719298,
+"Motion Properties Analysis": 23.046875
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 12.469211822660098,
+"level_2": 10.0,
+"level_3": 8.045977011494253,
+"relevance_score": 10.949337121212121,
+"relevance_linear_score": 23.626893939393938,
+"logic_score": 7.509157509157509,
+"total": 9.776841448189764
+},
+"second_head_rating": {
+"Physical World Reasoning": 5.357744107744107,
+"Video-Based Knowledge Acquisition": 9.468390804597702,
+"Complex Plot Comprehension": 8.81704980842912,
+"Temporal Reasoning": 8.257575757575758,
+"Order": 12.444444444444445,
+"Change": 10.336538461538462,
+"Social Behavior Analysis": 9.05,
+"Action &amp; Motion": 8.455882352941176,
+"Frame-Only": 12.947368421052632,
+"Frames &amp; Audio": 12.04861111111111
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 4.75,
+"Counterfactual Reasoning": 5.654761904761905,
+"Professional Knowledge Acquisition": 9.223484848484848,
+"High-Order Narrative Deconstruction": 6.23015873015873,
+"Symbolic/Metaphorical Interpretation": 10.080128205128204,
+"Narrative Turning Point Detection": 12.599206349206348,
+"Causal Reasoning": 7.200520833333334,
+"Event Sequence Ordering": 15.517241379310345,
+"Scene Transformation Detection": 13.020833333333334,
+"Entity Attribute Change Detection": 8.0,
+"Object Appearance Ordering": 13.194444444444445,
+"Individual Social Cognition": 6.583333333333334,
+"Collective Dynamics Analysis": 10.657051282051281,
+"General Skills Acquisition": 9.718992248062015,
+"Spatial Understanding": 4.4,
+"Counterintuitive Comprehension": 6.532738095238095,
+"Fine-Grained Action Recognition": 3.3333333333333335,
+"Visual Recognition": 25.526315789473685,
+"Dyadic Interaction Dynamics": 9.878472222222223,
+"Audio-Guided Visual Description": 10.5,
+"Narrative Cloze Inference": 5.767543859649123,
+"Future Event Prediction": 9.728260869565217,
+"Entity Existence Change Detection": 12.083333333333334,
+"Temporal Periodicity Detection": 6.688596491228071,
+"Repetitive Action Counting": 4.166666666666667,
+"Temporal Action Localization": 8.125,
+"Motion Trajectory Estimation": 10.416666666666666,
+"Basic Counting": 3.3653846153846154,
+"Numerical Calculation": 5.564516129032258,
+"Cross-Modal Semantic Consistency": 27.935606060606062,
+"Vision-Guided Audio Description": 5.706521739130435,
+"Visual-Audio Collaborative Reasoning": 7.708333333333334,
+"Motion Properties Analysis": 14.84375
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 18.058292282430216,
+"level_2": 12.725,
+"level_3": 13.136973180076629,
+"relevance_score": 13.636363636363637,
+"relevance_linear_score": 26.988636363636363,
+"logic_score": 15.453296703296703,
+"total": 14.25561797752809
+},
+"second_head_rating": {
+"Physical World Reasoning": 10.909090909090908,
+"Video-Based Knowledge Acquisition": 17.203065134099617,
+"Complex Plot Comprehension": 13.740421455938698,
+"Temporal Reasoning": 13.977272727272727,
+"Order": 16.083333333333332,
+"Change": 10.9375,
+"Social Behavior Analysis": 10.661111111111111,
+"Action &amp; Motion": 9.375,
+"Frame-Only": 14.013157894736842,
+"Frames &amp; Audio": 21.616512345679013
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 9.333333333333334,
+"Counterfactual Reasoning": 16.964285714285715,
+"Professional Knowledge Acquisition": 15.085227272727273,
+"High-Order Narrative Deconstruction": 13.373015873015872,
+"Symbolic/Metaphorical Interpretation": 13.557692307692308,
+"Narrative Turning Point Detection": 15.07936507936508,
+"Causal Reasoning": 14.934895833333334,
+"Event Sequence Ordering": 25.21551724137931,
+"Scene Transformation Detection": 12.5,
+"Entity Attribute Change Detection": 12.0,
+"Object Appearance Ordering": 13.194444444444445,
+"Individual Social Cognition": 15.083333333333332,
+"Collective Dynamics Analysis": 8.814102564102564,
+"General Skills Acquisition": 19.370155038759687,
+"Spatial Understanding": 5.15,
+"Counterintuitive Comprehension": 12.916666666666668,
+"Fine-Grained Action Recognition": 5.833333333333333,
+"Visual Recognition": 26.644736842105264,
+"Dyadic Interaction Dynamics": 8.055555555555555,
+"Audio-Guided Visual Description": 9.5,
+"Narrative Cloze Inference": 12.916666666666666,
+"Future Event Prediction": 12.644927536231883,
+"Entity Existence Change Detection": 7.916666666666667,
+"Temporal Periodicity Detection": 6.25,
+"Repetitive Action Counting": 3.125,
+"Temporal Action Localization": 8.125,
+"Motion Trajectory Estimation": 9.583333333333334,
+"Basic Counting": 4.8076923076923075,
+"Numerical Calculation": 6.25,
+"Cross-Modal Semantic Consistency": 28.977272727272727,
+"Vision-Guided Audio Description": 16.032608695652176,
+"Visual-Audio Collaborative Reasoning": 28.70614035087719,
+"Motion Properties Analysis": 17.96875
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 14.460180623973727,
+"level_2": 9.675,
+"level_3": 8.080699233716475,
+"relevance_score": 11.600378787878787,
+"relevance_linear_score": 24.242424242424242,
+"logic_score": 7.477106227106227,
+"total": 10.195068664169789
+},
+"second_head_rating": {
+"Physical World Reasoning": 4.953703703703704,
+"Video-Based Knowledge Acquisition": 8.67816091954023,
+"Complex Plot Comprehension": 11.695402298850574,
+"Temporal Reasoning": 6.5227272727272725,
+"Order": 11.216666666666667,
+"Change": 10.697115384615385,
+"Social Behavior Analysis": 7.322222222222222,
+"Action &amp; Motion": 9.742647058823529,
+"Frame-Only": 19.267543859649123,
+"Frames &amp; Audio": 10.231481481481481
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 5.5,
+"Counterfactual Reasoning": 2.6785714285714284,
+"Professional Knowledge Acquisition": 10.284090909090908,
+"High-Order Narrative Deconstruction": 9.107142857142858,
+"Symbolic/Metaphorical Interpretation": 19.214743589743588,
+"Narrative Turning Point Detection": 9.325396825396826,
+"Causal Reasoning": 6.015625,
+"Event Sequence Ordering": 10.775862068965518,
+"Scene Transformation Detection": 12.5,
+"Entity Attribute Change Detection": 12.5,
+"Object Appearance Ordering": 8.796296296296296,
+"Individual Social Cognition": 8.25,
+"Collective Dynamics Analysis": 4.551282051282051,
+"General Skills Acquisition": 7.034883720930233,
+"Spatial Understanding": 5.15,
+"Counterintuitive Comprehension": 5.997023809523809,
+"Fine-Grained Action Recognition": 5.0,
+"Visual Recognition": 33.91447368421053,
+"Dyadic Interaction Dynamics": 9.35763888888889,
+"Audio-Guided Visual Description": 11.0,
+"Narrative Cloze Inference": 6.885964912280702,
+"Future Event Prediction": 7.228260869565218,
+"Entity Existence Change Detection": 6.25,
+"Temporal Periodicity Detection": 15.328947368421053,
+"Repetitive Action Counting": 2.0833333333333335,
+"Temporal Action Localization": 5.625,
+"Motion Trajectory Estimation": 11.666666666666666,
+"Basic Counting": 10.576923076923077,
+"Numerical Calculation": 8.60215053763441,
+"Cross-Modal Semantic Consistency": 25.37878787878788,
+"Vision-Guided Audio Description": 2.717391304347826,
+"Visual-Audio Collaborative Reasoning": 5.504385964912281,
+"Motion Properties Analysis": 20.703125
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 19.045566502463053,
+"level_2": 12.218333333333334,
+"level_3": 11.728927203065133,
+"relevance_score": 14.180871212121213,
+"relevance_linear_score": 27.651515151515152,
+"logic_score": 12.875457875457876,
+"total": 13.735955056179776
+},
+"second_head_rating": {
+"Physical World Reasoning": 6.776094276094277,
+"Video-Based Knowledge Acquisition": 13.309386973180077,
+"Complex Plot Comprehension": 14.2911877394636,
+"Temporal Reasoning": 13.151515151515152,
+"Order": 16.083333333333332,
+"Change": 9.254807692307692,
+"Social Behavior Analysis": 13.461111111111112,
+"Action &amp; Motion": 9.466911764705882,
+"Frame-Only": 17.771929824561404,
+"Frames &amp; Audio": 20.165895061728392
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 4.75,
+"Counterfactual Reasoning": 6.25,
+"Professional Knowledge Acquisition": 13.854166666666668,
+"High-Order Narrative Deconstruction": 13.154761904761905,
+"Symbolic/Metaphorical Interpretation": 15.753205128205128,
+"Narrative Turning Point Detection": 18.5515873015873,
+"Causal Reasoning": 14.21875,
+"Event Sequence Ordering": 19.82758620689655,
+"Scene Transformation Detection": 9.375,
+"Entity Attribute Change Detection": 11.0,
+"Object Appearance Ordering": 13.657407407407407,
+"Individual Social Cognition": 14.833333333333332,
+"Collective Dynamics Analysis": 13.58974358974359,
+"General Skills Acquisition": 12.751937984496125,
+"Spatial Understanding": 6.8,
+"Counterintuitive Comprehension": 8.958333333333334,
+"Fine-Grained Action Recognition": 3.75,
+"Visual Recognition": 33.0921052631579,
+"Dyadic Interaction Dynamics": 11.892361111111112,
+"Audio-Guided Visual Description": 10.0,
+"Narrative Cloze Inference": 8.837719298245613,
+"Future Event Prediction": 11.666666666666666,
+"Entity Existence Change Detection": 6.25,
+"Temporal Periodicity Detection": 13.81578947368421,
+"Repetitive Action Counting": 2.6041666666666665,
+"Temporal Action Localization": 5.0,
+"Motion Trajectory Estimation": 13.75,
+"Basic Counting": 8.173076923076923,
+"Numerical Calculation": 7.043010752688172,
+"Cross-Modal Semantic Consistency": 29.35606060606061,
+"Vision-Guided Audio Description": 14.402173913043478,
+"Visual-Audio Collaborative Reasoning": 25.021929824561404,
+"Motion Properties Analysis": 18.75
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 12.842775041050905,
+"level_2": 5.658333333333333,
+"level_3": 5.483716475095785,
+"relevance_score": 8.581912878787879,
+"relevance_linear_score": 19.270833333333332,
+"logic_score": 5.123626373626373,
+"total": 7.403245942571785
+},
+"second_head_rating": {
+"Physical World Reasoning": 4.044612794612795,
+"Video-Based Knowledge Acquisition": 5.325670498084291,
+"Complex Plot Comprehension": 5.354406130268199,
+"Temporal Reasoning": 4.015151515151516,
+"Order": 6.666666666666667,
+"Change": 3.8461538461538463,
+"Social Behavior Analysis": 7.716666666666667,
+"Action &amp; Motion": 7.261029411764706,
+"Frame-Only": 16.75438596491228,
+"Frames &amp; Audio": 9.402006172839506
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 3.0,
+"Counterfactual Reasoning": 4.166666666666667,
+"Professional Knowledge Acquisition": 5.198863636363637,
+"High-Order Narrative Deconstruction": 4.345238095238095,
+"Symbolic/Metaphorical Interpretation": 7.772435897435898,
+"Narrative Turning Point Detection": 6.25,
+"Causal Reasoning": 3.5026041666666665,
+"Event Sequence Ordering": 8.620689655172415,
+"Scene Transformation Detection": 5.729166666666667,
+"Entity Attribute Change Detection": 4.5,
+"Object Appearance Ordering": 5.324074074074074,
+"Individual Social Cognition": 7.833333333333334,
+"Collective Dynamics Analysis": 6.634615384615385,
+"General Skills Acquisition": 5.455426356589148,
+"Spatial Understanding": 5.55,
+"Counterintuitive Comprehension": 3.541666666666667,
+"Fine-Grained Action Recognition": 4.166666666666667,
+"Visual Recognition": 34.703947368421055,
+"Dyadic Interaction Dynamics": 8.76736111111111,
+"Audio-Guided Visual Description": 9.0,
+"Narrative Cloze Inference": 2.1710526315789473,
+"Future Event Prediction": 4.728260869565218,
+"Entity Existence Change Detection": 1.25,
+"Temporal Periodicity Detection": 5.592105263157895,
+"Repetitive Action Counting": 5.729166666666667,
+"Temporal Action Localization": 5.0,
+"Motion Trajectory Estimation": 7.916666666666667,
+"Basic Counting": 6.490384615384615,
+"Numerical Calculation": 3.360215053763441,
+"Cross-Modal Semantic Consistency": 23.011363636363637,
+"Vision-Guided Audio Description": 2.989130434782609,
+"Visual-Audio Collaborative Reasoning": 5.668859649122807,
+"Motion Properties Analysis": 12.109375
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 16.042692939244663,
+"level_2": 6.86,
+"level_3": 7.224616858237548,
+"relevance_score": 10.262784090909092,
+"relevance_linear_score": 22.111742424242426,
+"logic_score": 7.571733821733822,
+"total": 9.345609654598418
+},
+"second_head_rating": {
+"Physical World Reasoning": 5.202020202020202,
+"Video-Based Knowledge Acquisition": 8.82662835249042,
+"Complex Plot Comprehension": 6.015325670498084,
+"Temporal Reasoning": 6.484848484848485,
+"Order": 6.944444444444445,
+"Change": 4.5673076923076925,
+"Social Behavior Analysis": 9.438888888888888,
+"Action &amp; Motion": 8.823529411764707,
+"Frame-Only": 17.719298245614034,
+"Frames &amp; Audio": 14.5679012345679
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 3.5,
+"Counterfactual Reasoning": 5.654761904761905,
+"Professional Knowledge Acquisition": 8.636363636363637,
+"High-Order Narrative Deconstruction": 4.523809523809524,
+"Symbolic/Metaphorical Interpretation": 8.397435897435898,
+"Narrative Turning Point Detection": 7.043650793650794,
+"Causal Reasoning": 6.197916666666667,
+"Event Sequence Ordering": 8.836206896551724,
+"Scene Transformation Detection": 5.729166666666667,
+"Entity Attribute Change Detection": 6.25,
+"Object Appearance Ordering": 5.092592592592593,
+"Individual Social Cognition": 14.833333333333332,
+"Collective Dynamics Analysis": 5.673076923076923,
+"General Skills Acquisition": 9.021317829457365,
+"Spatial Understanding": 5.3,
+"Counterintuitive Comprehension": 6.294642857142857,
+"Fine-Grained Action Recognition": 4.166666666666667,
+"Visual Recognition": 35.0328947368421,
+"Dyadic Interaction Dynamics": 7.899305555555556,
+"Audio-Guided Visual Description": 10.25,
+"Narrative Cloze Inference": 3.267543859649123,
+"Future Event Prediction": 6.884057971014493,
+"Entity Existence Change Detection": 0.8333333333333334,
+"Temporal Periodicity Detection": 6.688596491228071,
+"Repetitive Action Counting": 6.770833333333333,
+"Temporal Action Localization": 6.875,
+"Motion Trajectory Estimation": 10.0,
+"Basic Counting": 9.85576923076923,
+"Numerical Calculation": 3.091397849462366,
+"Cross-Modal Semantic Consistency": 24.431818181818183,
+"Vision-Guided Audio Description": 5.163043478260869,
+"Visual-Audio Collaborative Reasoning": 17.390350877192983,
+"Motion Properties Analysis": 14.84375
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 14.638752052545156,
+"level_2": 9.896666666666667,
+"level_3": 6.791187739463602,
+"relevance_score": 11.446496212121213,
+"relevance_linear_score": 24.289772727272727,
+"logic_score": 6.466727716727717,
+"total": 9.749271743653766
+},
+"second_head_rating": {
+"Physical World Reasoning": 4.608585858585859,
+"Video-Based Knowledge Acquisition": 7.64367816091954,
+"Complex Plot Comprehension": 7.878352490421456,
+"Temporal Reasoning": 6.765151515151515,
+"Order": 11.777777777777779,
+"Change": 8.774038461538462,
+"Social Behavior Analysis": 7.422222222222222,
+"Action &amp; Motion": 11.213235294117647,
+"Frame-Only": 16.460526315789473,
+"Frames &amp; Audio": 13.036265432098766
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 5.9,
+"Counterfactual Reasoning": 3.1547619047619047,
+"Professional Knowledge Acquisition": 8.607954545454545,
+"High-Order Narrative Deconstruction": 6.607142857142857,
+"Symbolic/Metaphorical Interpretation": 11.506410256410257,
+"Narrative Turning Point Detection": 9.126984126984128,
+"Causal Reasoning": 4.596354166666667,
+"Event Sequence Ordering": 14.870689655172415,
+"Scene Transformation Detection": 7.8125,
+"Entity Attribute Change Detection": 8.75,
+"Object Appearance Ordering": 11.574074074074074,
+"Individual Social Cognition": 10.5,
+"Collective Dynamics Analysis": 6.0576923076923075,
+"General Skills Acquisition": 6.656976744186046,
+"Spatial Understanding": 4.8,
+"Counterintuitive Comprehension": 4.375,
+"Fine-Grained Action Recognition": 3.75,
+"Visual Recognition": 32.10526315789474,
+"Dyadic Interaction Dynamics": 5.694444444444444,
+"Audio-Guided Visual Description": 20.5,
+"Narrative Cloze Inference": 2.93859649122807,
+"Future Event Prediction": 9.782608695652174,
+"Entity Existence Change Detection": 9.583333333333334,
+"Temporal Periodicity Detection": 7.3464912280701755,
+"Repetitive Action Counting": 12.5,
+"Temporal Action Localization": 10.0,
+"Motion Trajectory Estimation": 16.25,
+"Basic Counting": 6.25,
+"Numerical Calculation": 5.846774193548387,
+"Cross-Modal Semantic Consistency": 18.276515151515152,
+"Vision-Guided Audio Description": 6.25,
+"Visual-Audio Collaborative Reasoning": 9.199561403508772,
+"Motion Properties Analysis": 13.28125
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 21.15968801313629,
+"level_2": 13.606666666666666,
+"level_3": 11.403256704980844,
+"relevance_score": 14.666193181818182,
+"relevance_linear_score": 28.740530303030305,
+"logic_score": 14.365079365079364,
+"total": 14.563566375364127
+},
+"second_head_rating": {
+"Physical World Reasoning": 8.383838383838384,
+"Video-Based Knowledge Acquisition": 13.572796934865899,
+"Complex Plot Comprehension": 10.522030651340996,
+"Temporal Reasoning": 15.03030303030303,
+"Order": 16.083333333333332,
+"Change": 10.216346153846153,
+"Social Behavior Analysis": 13.894444444444444,
+"Action &amp; Motion": 12.316176470588236,
+"Frame-Only": 19.00438596491228,
+"Frames &amp; Audio": 23.055555555555557
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 11.05,
+"Counterfactual Reasoning": 11.488095238095237,
+"Professional Knowledge Acquisition": 14.753787878787877,
+"High-Order Narrative Deconstruction": 10.297619047619047,
+"Symbolic/Metaphorical Interpretation": 13.141025641025642,
+"Narrative Turning Point Detection": 12.400793650793652,
+"Causal Reasoning": 14.869791666666666,
+"Event Sequence Ordering": 23.060344827586206,
+"Scene Transformation Detection": 7.8125,
+"Entity Attribute Change Detection": 11.0,
+"Object Appearance Ordering": 13.88888888888889,
+"Individual Social Cognition": 23.083333333333336,
+"Collective Dynamics Analysis": 10.705128205128204,
+"General Skills Acquisition": 12.364341085271317,
+"Spatial Understanding": 3.9,
+"Counterintuitive Comprehension": 7.678571428571429,
+"Fine-Grained Action Recognition": 7.5,
+"Visual Recognition": 35.06578947368421,
+"Dyadic Interaction Dynamics": 7.777777777777778,
+"Audio-Guided Visual Description": 22.0,
+"Narrative Cloze Inference": 5.109649122807017,
+"Future Event Prediction": 15.253623188405797,
+"Entity Existence Change Detection": 10.833333333333334,
+"Temporal Periodicity Detection": 8.552631578947368,
+"Repetitive Action Counting": 11.979166666666666,
+"Temporal Action Localization": 15.0,
+"Motion Trajectory Estimation": 15.0,
+"Basic Counting": 7.6923076923076925,
+"Numerical Calculation": 8.803763440860216,
+"Cross-Modal Semantic Consistency": 17.708333333333332,
+"Vision-Guided Audio Description": 21.467391304347824,
+"Visual-Audio Collaborative Reasoning": 27.80701754385965,
+"Motion Properties Analysis": 12.890625
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 20.01231527093596,
+"level_2": 20.915,
+"level_3": 14.698275862068966,
+"relevance_score": 17.258522727272727,
+"relevance_linear_score": 31.060606060606062,
+"logic_score": 19.391025641025642,
+"total": 17.98533083645443
+},
+"second_head_rating": {
+"Physical World Reasoning": 9.772727272727273,
+"Video-Based Knowledge Acquisition": 20.751915708812263,
+"Complex Plot Comprehension": 15.914750957854405,
+"Temporal Reasoning": 24.045454545454547,
+"Order": 31.916666666666668,
+"Change": 15.504807692307692,
+"Social Behavior Analysis": 12.766666666666667,
+"Action &amp; Motion": 10.386029411764707,
+"Frame-Only": 14.328947368421053,
+"Frames &amp; Audio": 25.011574074074073
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 11.9,
+"Counterfactual Reasoning": 7.738095238095238,
+"Professional Knowledge Acquisition": 23.4280303030303,
+"High-Order Narrative Deconstruction": 7.678571428571429,
+"Symbolic/Metaphorical Interpretation": 26.10576923076923,
+"Narrative Turning Point Detection": 12.202380952380953,
+"Causal Reasoning": 25.611979166666668,
+"Event Sequence Ordering": 40.08620689655172,
+"Scene Transformation Detection": 18.75,
+"Entity Attribute Change Detection": 15.0,
+"Object Appearance Ordering": 30.09259259259259,
+"Individual Social Cognition": 16.333333333333332,
+"Collective Dynamics Analysis": 11.137820512820513,
+"General Skills Acquisition": 18.01356589147287,
+"Spatial Understanding": 5.4,
+"Counterintuitive Comprehension": 13.303571428571429,
+"Fine-Grained Action Recognition": 2.5,
+"Visual Recognition": 23.55263157894737,
+"Dyadic Interaction Dynamics": 10.815972222222221,
+"Audio-Guided Visual Description": 10.5,
+"Narrative Cloze Inference": 15.175438596491228,
+"Future Event Prediction": 21.865942028985508,
+"Entity Existence Change Detection": 13.75,
+"Temporal Periodicity Detection": 22.039473684210527,
+"Repetitive Action Counting": 10.9375,
+"Temporal Action Localization": 6.875,
+"Motion Trajectory Estimation": 9.583333333333334,
+"Basic Counting": 7.9326923076923075,
+"Numerical Calculation": 8.387096774193548,
+"Cross-Modal Semantic Consistency": 24.526515151515152,
+"Vision-Guided Audio Description": 22.282608695652176,
+"Visual-Audio Collaborative Reasoning": 36.49122807017544,
+"Motion Properties Analysis": 20.3125
+}
+}</t>
+  </si>
+  <si>
+    <t>25/62</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 17.71551724137931,
+"level_2": 11.92,
+"level_3": 8.52610153256705,
+"relevance_score": 13.008996212121213,
+"relevance_linear_score": 25.615530303030305,
+"logic_score": 9.797008547008547,
+"total": 11.914273824386184
+},
+"second_head_rating": {
+"Physical World Reasoning": 4.848484848484849,
+"Video-Based Knowledge Acquisition": 12.298850574712644,
+"Complex Plot Comprehension": 9.24808429118774,
+"Temporal Reasoning": 10.25,
+"Order": 16.25,
+"Change": 9.735576923076923,
+"Social Behavior Analysis": 8.166666666666666,
+"Action &amp; Motion": 10.165441176470589,
+"Frame-Only": 21.223684210526315,
+"Frames &amp; Audio": 14.62962962962963
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 4.75,
+"Counterfactual Reasoning": 4.464285714285714,
+"Professional Knowledge Acquisition": 16.193181818181817,
+"High-Order Narrative Deconstruction": 3.75,
+"Symbolic/Metaphorical Interpretation": 14.326923076923077,
+"Narrative Turning Point Detection": 11.21031746031746,
+"Causal Reasoning": 11.484375,
+"Event Sequence Ordering": 18.96551724137931,
+"Scene Transformation Detection": 13.020833333333334,
+"Entity Attribute Change Detection": 11.0,
+"Object Appearance Ordering": 13.657407407407407,
+"Individual Social Cognition": 10.333333333333332,
+"Collective Dynamics Analysis": 4.5673076923076925,
+"General Skills Acquisition": 8.313953488372093,
+"Spatial Understanding": 3.4,
+"Counterintuitive Comprehension": 6.517857142857143,
+"Fine-Grained Action Recognition": 7.75,
+"Visual Recognition": 40.06578947368421,
+"Dyadic Interaction Dynamics": 9.809027777777777,
+"Audio-Guided Visual Description": 11.25,
+"Narrative Cloze Inference": 6.2061403508771935,
+"Future Event Prediction": 8.532608695652174,
+"Entity Existence Change Detection": 5.0,
+"Temporal Periodicity Detection": 15.789473684210526,
+"Repetitive Action Counting": 6.770833333333333,
+"Temporal Action Localization": 11.25,
+"Motion Trajectory Estimation": 14.166666666666666,
+"Basic Counting": 7.6923076923076925,
+"Numerical Calculation": 9.475806451612904,
+"Cross-Modal Semantic Consistency": 34.46969696969697,
+"Vision-Guided Audio Description": 7.065217391304348,
+"Visual-Audio Collaborative Reasoning": 9.945175438596491,
+"Motion Properties Analysis": 10.546875
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 21.972495894909688,
+"level_2": 15.458333333333334,
+"level_3": 12.63050766283525,
+"relevance_score": 16.228693181818183,
+"relevance_linear_score": 30.634469696969695,
+"logic_score": 15.207570207570209,
+"total": 15.880669995838534
+},
+"second_head_rating": {
+"Physical World Reasoning": 9.086700336700337,
+"Video-Based Knowledge Acquisition": 18.477011494252874,
+"Complex Plot Comprehension": 12.567049808429118,
+"Temporal Reasoning": 17.583333333333336,
+"Order": 19.5,
+"Change": 13.822115384615385,
+"Social Behavior Analysis": 10.6,
+"Action &amp; Motion": 10.533088235294118,
+"Frame-Only": 20.364035087719298,
+"Frames &amp; Audio": 23.38734567901235
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 12.483333333333333,
+"Counterfactual Reasoning": 7.142857142857143,
+"Professional Knowledge Acquisition": 20.303030303030305,
+"High-Order Narrative Deconstruction": 7.7976190476190474,
+"Symbolic/Metaphorical Interpretation": 19.743589743589745,
+"Narrative Turning Point Detection": 13.392857142857142,
+"Causal Reasoning": 18.125,
+"Event Sequence Ordering": 21.336206896551722,
+"Scene Transformation Detection": 17.708333333333332,
+"Entity Attribute Change Detection": 17.0,
+"Object Appearance Ordering": 20.60185185185185,
+"Individual Social Cognition": 16.083333333333332,
+"Collective Dynamics Analysis": 6.25,
+"General Skills Acquisition": 16.608527131782946,
+"Spatial Understanding": 3.9,
+"Counterintuitive Comprehension": 12.142857142857142,
+"Fine-Grained Action Recognition": 6.5,
+"Visual Recognition": 35.46052631578947,
+"Dyadic Interaction Dynamics": 9.600694444444445,
+"Audio-Guided Visual Description": 15.0,
+"Narrative Cloze Inference": 7.105263157894737,
+"Future Event Prediction": 16.829710144927535,
+"Entity Existence Change Detection": 5.416666666666667,
+"Temporal Periodicity Detection": 15.131578947368421,
+"Repetitive Action Counting": 5.208333333333333,
+"Temporal Action Localization": 15.0,
+"Motion Trajectory Estimation": 12.916666666666666,
+"Basic Counting": 5.288461538461538,
+"Numerical Calculation": 14.50268817204301,
+"Cross-Modal Semantic Consistency": 33.333333333333336,
+"Vision-Guided Audio Description": 14.402173913043478,
+"Visual-Audio Collaborative Reasoning": 28.585526315789473,
+"Motion Properties Analysis": 13.28125
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 15.192939244663382,
+"level_2": 11.901666666666666,
+"level_3": 9.47198275862069,
+"relevance_score": 12.855113636363637,
+"relevance_linear_score": 26.325757575757574,
+"logic_score": 9.407814407814408,
+"total": 11.68019142738244
+},
+"second_head_rating": {
+"Physical World Reasoning": 5.4840067340067336,
+"Video-Based Knowledge Acquisition": 14.224137931034482,
+"Complex Plot Comprehension": 10.196360153256705,
+"Temporal Reasoning": 9.303030303030303,
+"Order": 16.133333333333333,
+"Change": 13.461538461538462,
+"Social Behavior Analysis": 8.383333333333333,
+"Action &amp; Motion": 8.143382352941176,
+"Frame-Only": 16.403508771929825,
+"Frames &amp; Audio": 14.128086419753085
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 6.0,
+"Counterfactual Reasoning": 4.166666666666667,
+"Professional Knowledge Acquisition": 16.837121212121215,
+"High-Order Narrative Deconstruction": 7.7976190476190474,
+"Symbolic/Metaphorical Interpretation": 16.233974358974358,
+"Narrative Turning Point Detection": 11.40873015873016,
+"Causal Reasoning": 7.395833333333334,
+"Event Sequence Ordering": 18.53448275862069,
+"Scene Transformation Detection": 21.354166666666668,
+"Entity Attribute Change Detection": 12.25,
+"Object Appearance Ordering": 16.435185185185187,
+"Individual Social Cognition": 9.333333333333334,
+"Collective Dynamics Analysis": 7.6923076923076925,
+"General Skills Acquisition": 11.550387596899226,
+"Spatial Understanding": 2.9,
+"Counterintuitive Comprehension": 8.318452380952381,
+"Fine-Grained Action Recognition": 2.3333333333333335,
+"Visual Recognition": 30.75657894736842,
+"Dyadic Interaction Dynamics": 8.14236111111111,
+"Audio-Guided Visual Description": 13.0,
+"Narrative Cloze Inference": 3.2456140350877196,
+"Future Event Prediction": 11.956521739130435,
+"Entity Existence Change Detection": 9.166666666666666,
+"Temporal Periodicity Detection": 12.039473684210526,
+"Repetitive Action Counting": 6.25,
+"Temporal Action Localization": 9.375,
+"Motion Trajectory Estimation": 10.0,
+"Basic Counting": 5.288461538461538,
+"Numerical Calculation": 8.131720430107528,
+"Cross-Modal Semantic Consistency": 32.765151515151516,
+"Vision-Guided Audio Description": 6.521739130434782,
+"Visual-Audio Collaborative Reasoning": 8.68421052631579,
+"Motion Properties Analysis": 12.5
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 23.177339901477833,
+"level_2": 18.515,
+"level_3": 16.050047892720308,
+"relevance_score": 18.276515151515152,
+"relevance_linear_score": 32.95454545454545,
+"logic_score": 19.3009768009768,
+"total": 18.625676238035787
+},
+"second_head_rating": {
+"Physical World Reasoning": 10.244107744107744,
+"Video-Based Knowledge Acquisition": 25.14367816091954,
+"Complex Plot Comprehension": 15.627394636015325,
+"Temporal Reasoning": 22.613636363636363,
+"Order": 24.133333333333333,
+"Change": 15.625,
+"Social Behavior Analysis": 13.655555555555557,
+"Action &amp; Motion": 11.213235294117647,
+"Frame-Only": 20.657894736842106,
+"Frames &amp; Audio": 25.39351851851852
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 12.65,
+"Counterfactual Reasoning": 12.202380952380953,
+"Professional Knowledge Acquisition": 27.575757575757574,
+"High-Order Narrative Deconstruction": 10.178571428571429,
+"Symbolic/Metaphorical Interpretation": 17.259615384615383,
+"Narrative Turning Point Detection": 19.543650793650794,
+"Causal Reasoning": 22.278645833333332,
+"Event Sequence Ordering": 34.69827586206897,
+"Scene Transformation Detection": 19.791666666666668,
+"Entity Attribute Change Detection": 15.75,
+"Object Appearance Ordering": 22.685185185185187,
+"Individual Social Cognition": 20.333333333333332,
+"Collective Dynamics Analysis": 10.096153846153847,
+"General Skills Acquisition": 22.655038759689923,
+"Spatial Understanding": 3.9,
+"Counterintuitive Comprehension": 12.291666666666668,
+"Fine-Grained Action Recognition": 5.416666666666667,
+"Visual Recognition": 34.86842105263158,
+"Dyadic Interaction Dynamics": 10.555555555555555,
+"Audio-Guided Visual Description": 11.0,
+"Narrative Cloze Inference": 15.087719298245615,
+"Future Event Prediction": 23.07971014492754,
+"Entity Existence Change Detection": 12.083333333333334,
+"Temporal Periodicity Detection": 10.06578947368421,
+"Repetitive Action Counting": 4.166666666666667,
+"Temporal Action Localization": 18.125,
+"Motion Trajectory Estimation": 10.833333333333334,
+"Basic Counting": 9.85576923076923,
+"Numerical Calculation": 12.298387096774194,
+"Cross-Modal Semantic Consistency": 23.674242424242426,
+"Vision-Guided Audio Description": 28.532608695652176,
+"Visual-Audio Collaborative Reasoning": 33.958333333333336,
+"Motion Properties Analysis": 17.96875
+}
+}</t>
   </si>
 </sst>
 </file>
@@ -2008,7 +3136,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2016,7 +3143,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2026,7 +3152,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2034,7 +3159,6 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2794,43 +3918,55 @@
       <c r="B15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>38</v>
-      </c>
+      <c r="C15" s="4">
+        <v>14</v>
+      </c>
+      <c r="D15" s="4">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="E15" s="4">
+        <v>28.7</v>
+      </c>
+      <c r="F15" s="4">
+        <v>30.2</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" s="4"/>
+      <c r="I15" s="3"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A16" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>38</v>
-      </c>
+      <c r="C16" s="4">
+        <v>21.8</v>
+      </c>
+      <c r="D16" s="4">
+        <v>45.5</v>
+      </c>
+      <c r="E16" s="4">
+        <v>36.1</v>
+      </c>
+      <c r="F16" s="4">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H16" s="4"/>
+      <c r="I16" s="3"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>41</v>
       </c>
       <c r="C17" s="4">
         <v>9.9</v>
@@ -2845,17 +3981,17 @@
         <v>25</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="3"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" s="4">
         <v>14.6</v>
@@ -2870,17 +4006,17 @@
         <v>31.7</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="3"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C19" s="4">
         <v>11.2</v>
@@ -2895,17 +4031,17 @@
         <v>26.7</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="3"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20" s="4">
         <v>16.100000000000001</v>
@@ -2920,17 +4056,17 @@
         <v>33.1</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="3"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" s="4">
         <v>8</v>
@@ -2945,17 +4081,17 @@
         <v>21.4</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="3"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" s="4">
         <v>15.5</v>
@@ -2970,244 +4106,352 @@
         <v>32.799999999999997</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="3"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>55</v>
-      </c>
+      <c r="C23" s="4">
+        <v>15.5</v>
+      </c>
+      <c r="D23" s="4">
+        <v>37.5</v>
+      </c>
+      <c r="E23" s="4">
+        <v>31.3</v>
+      </c>
+      <c r="F23" s="4">
+        <v>33.4</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H23" s="4"/>
+      <c r="I23" s="3"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>57</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="C24" s="4">
+        <v>21.8</v>
+      </c>
+      <c r="D24" s="4">
+        <v>47.2</v>
+      </c>
+      <c r="E24" s="4">
+        <v>37.4</v>
+      </c>
+      <c r="F24" s="4">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="H24" s="4"/>
+      <c r="I24" s="3"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>60</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C25" s="4">
+        <v>15.1</v>
+      </c>
+      <c r="D25" s="4">
+        <v>33.6</v>
+      </c>
+      <c r="E25" s="4">
+        <v>31</v>
+      </c>
+      <c r="F25" s="4">
+        <v>31.9</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="H25" s="4"/>
+      <c r="I25" s="3"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>60</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C26" s="4">
+        <v>19</v>
+      </c>
+      <c r="D26" s="4">
+        <v>41.9</v>
+      </c>
+      <c r="E26" s="4">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="F26" s="4">
+        <v>37.6</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="H26" s="4"/>
+      <c r="I26" s="3"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A27" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="5"/>
+        <v>61</v>
+      </c>
+      <c r="C27" s="4">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="D27" s="4">
+        <v>26.4</v>
+      </c>
+      <c r="E27" s="4">
+        <v>23.6</v>
+      </c>
+      <c r="F27" s="4">
+        <v>24.6</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>119</v>
+      </c>
       <c r="H27" s="4"/>
-      <c r="I27" s="3" t="s">
-        <v>64</v>
-      </c>
+      <c r="I27" s="3"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="5"/>
+        <v>61</v>
+      </c>
+      <c r="C28" s="4">
+        <v>14.3</v>
+      </c>
+      <c r="D28" s="4">
+        <v>36.5</v>
+      </c>
+      <c r="E28" s="4">
+        <v>27</v>
+      </c>
+      <c r="F28" s="4">
+        <v>30.2</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>120</v>
+      </c>
       <c r="H28" s="4"/>
-      <c r="I28" s="3" t="s">
-        <v>64</v>
-      </c>
+      <c r="I28" s="3"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="5"/>
+        <v>64</v>
+      </c>
+      <c r="C29" s="4">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D29" s="4">
+        <v>26.8</v>
+      </c>
+      <c r="E29" s="4">
+        <v>24.2</v>
+      </c>
+      <c r="F29" s="4">
+        <v>25.1</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>121</v>
+      </c>
       <c r="H29" s="4"/>
       <c r="I29" s="3"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A30" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="5"/>
+        <v>64</v>
+      </c>
+      <c r="C30" s="4">
+        <v>13.7</v>
+      </c>
+      <c r="D30" s="4">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="E30" s="4">
+        <v>27.7</v>
+      </c>
+      <c r="F30" s="4">
+        <v>30.6</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>122</v>
+      </c>
       <c r="H30" s="4"/>
       <c r="I30" s="3"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A31" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="5"/>
+        <v>67</v>
+      </c>
+      <c r="C31" s="4">
+        <v>7.4</v>
+      </c>
+      <c r="D31" s="4">
+        <v>21</v>
+      </c>
+      <c r="E31" s="4">
+        <v>19.3</v>
+      </c>
+      <c r="F31" s="4">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>123</v>
+      </c>
       <c r="H31" s="4"/>
       <c r="I31" s="3"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A32" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="5"/>
+        <v>67</v>
+      </c>
+      <c r="C32" s="4">
+        <v>9.4</v>
+      </c>
+      <c r="D32" s="4">
+        <v>27.4</v>
+      </c>
+      <c r="E32" s="4">
+        <v>22.1</v>
+      </c>
+      <c r="F32" s="4">
+        <v>23.9</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>124</v>
+      </c>
       <c r="H32" s="4"/>
       <c r="I32" s="3"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A33" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="5"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="3"/>
+      <c r="H33" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A34" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="5"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="3"/>
+      <c r="H34" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A35" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="5"/>
+        <v>73</v>
+      </c>
+      <c r="C35" s="4">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="D35" s="4">
+        <v>27.4</v>
+      </c>
+      <c r="E35" s="4">
+        <v>24.3</v>
+      </c>
+      <c r="F35" s="4">
+        <v>25.3</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>125</v>
+      </c>
       <c r="H35" s="4"/>
-      <c r="I35" s="3"/>
+      <c r="I35" s="4"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A36" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="5"/>
+        <v>73</v>
+      </c>
+      <c r="C36" s="4">
+        <v>14.6</v>
+      </c>
+      <c r="D36" s="4">
+        <v>37.4</v>
+      </c>
+      <c r="E36" s="4">
+        <v>28.7</v>
+      </c>
+      <c r="F36" s="4">
+        <v>31.7</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>126</v>
+      </c>
       <c r="H36" s="4"/>
       <c r="I36" s="3"/>
     </row>
     <row r="37" spans="1:9" ht="15" x14ac:dyDescent="0.4">
       <c r="A37" s="11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
@@ -3220,10 +4464,10 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A38" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C38" s="4">
         <v>11.2</v>
@@ -3238,17 +4482,17 @@
         <v>25.7</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C39" s="4">
         <v>18.8</v>
@@ -3263,17 +4507,17 @@
         <v>35.6</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C40" s="4">
         <v>12.2</v>
@@ -3288,17 +4532,17 @@
         <v>26.8</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A41" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C41" s="6">
         <v>20.3</v>
@@ -3313,17 +4557,17 @@
         <v>37.200000000000003</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H41" s="4"/>
       <c r="I41" s="6"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A42" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C42" s="4">
         <v>12.3</v>
@@ -3338,34 +4582,42 @@
         <v>28.37</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>91</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="H42" s="4"/>
       <c r="I42" s="4"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="5"/>
+        <v>86</v>
+      </c>
+      <c r="C43" s="4">
+        <v>18</v>
+      </c>
+      <c r="D43" s="4">
+        <v>39.1</v>
+      </c>
+      <c r="E43" s="4">
+        <v>31.1</v>
+      </c>
+      <c r="F43" s="4">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>127</v>
+      </c>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A44" s="6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C44" s="6">
         <v>18.5</v>
@@ -3380,17 +4632,17 @@
         <v>36.1</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A45" s="6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C45" s="6">
         <v>19.899999999999999</v>
@@ -3405,17 +4657,17 @@
         <v>38.1</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A46" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C46" s="6">
         <v>15.7</v>
@@ -3430,17 +4682,17 @@
         <v>33</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A47" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C47" s="6">
         <v>25.8</v>
@@ -3455,85 +4707,117 @@
         <v>43.8</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A48" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="5"/>
+        <v>99</v>
+      </c>
+      <c r="C48" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="D48" s="4">
+        <v>29.9</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F48" s="4">
+        <v>27.1</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>129</v>
+      </c>
       <c r="H48" s="4"/>
-      <c r="I48" s="4" t="s">
-        <v>104</v>
-      </c>
+      <c r="I48" s="4"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A49" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="5"/>
+        <v>99</v>
+      </c>
+      <c r="C49" s="4">
+        <v>15.9</v>
+      </c>
+      <c r="D49" s="4">
+        <v>37.1</v>
+      </c>
+      <c r="E49" s="4">
+        <v>30.6</v>
+      </c>
+      <c r="F49" s="4">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>130</v>
+      </c>
       <c r="H49" s="4"/>
-      <c r="I49" s="4" t="s">
-        <v>104</v>
-      </c>
+      <c r="I49" s="4"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A50" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4" t="s">
-        <v>64</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="C50" s="4">
+        <v>11.7</v>
+      </c>
+      <c r="D50" s="4">
+        <v>29.4</v>
+      </c>
+      <c r="E50" s="4">
+        <v>26.3</v>
+      </c>
+      <c r="F50" s="4">
+        <v>27.4</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="H50" s="3"/>
+      <c r="I50" s="4"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A51" s="4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="5"/>
+        <v>102</v>
+      </c>
+      <c r="C51" s="4">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="D51" s="4">
+        <v>41.3</v>
+      </c>
+      <c r="E51" s="4">
+        <v>33</v>
+      </c>
+      <c r="F51" s="4">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="H51" s="4"/>
-      <c r="I51" s="4" t="s">
-        <v>64</v>
-      </c>
+      <c r="I51" s="4"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A52" s="4" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
@@ -3545,10 +4829,10 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A53" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
@@ -3560,10 +4844,10 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A54" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
@@ -3575,10 +4859,10 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A55" s="4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
@@ -3590,10 +4874,10 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A56" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
@@ -3605,10 +4889,10 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A57" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>

--- a/figs/exps/performance.xlsx
+++ b/figs/exps/performance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\GitHub\VideoMMEv2\figs\exps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516D56E3-7C7D-4CD3-BDE6-ADE56BFDACF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A1ABB7-9B9C-4F32-B4FC-AEA5233B5F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2880" yWindow="2880" windowWidth="17280" windowHeight="10523" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="140">
   <si>
     <t>模型</t>
   </si>
@@ -835,9 +835,6 @@
     <t>Qwen2_5-VL-72B-Instruct</t>
   </si>
   <si>
-    <t>在推</t>
-  </si>
-  <si>
     <t>Qwen2_5-VL-72B-Instruct-sub</t>
   </si>
   <si>
@@ -1234,9 +1231,6 @@
 max_tokens: 16384</t>
   </si>
   <si>
-    <t>H20_2</t>
-  </si>
-  <si>
     <t>InternVL3_5-241B-A28B-Instruct-sub</t>
   </si>
   <si>
@@ -1245,9 +1239,6 @@
   <si>
     <t>temperature: 0.2
 max_tokens: 2048</t>
-  </si>
-  <si>
-    <t>H20_3</t>
   </si>
   <si>
     <t>KimiVL-16B-A3B-Instruct-sub</t>
@@ -3108,6 +3099,492 @@
 "Vision-Guided Audio Description": 28.532608695652176,
 "Visual-Audio Collaborative Reasoning": 33.958333333333336,
 "Motion Properties Analysis": 17.96875
+}
+}</t>
+  </si>
+  <si>
+    <t>Frame</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 15.492610837438423,
+"level_2": 11.096666666666666,
+"level_3": 9.256465517241379,
+"relevance_score": 12.914299242424242,
+"relevance_linear_score": 26.27840909090909,
+"logic_score": 8.504273504273504,
+"total": 11.411256762380358
+},
+"second_head_rating": {
+"Physical World Reasoning": 6.346801346801347,
+"Video-Based Knowledge Acquisition": 10.938697318007662,
+"Complex Plot Comprehension": 10.871647509578544,
+"Temporal Reasoning": 6.348484848484849,
+"Order": 14.583333333333334,
+"Change": 9.375,
+"Social Behavior Analysis": 9.272222222222222,
+"Action &amp; Motion": 12.408088235294118,
+"Frame-Only": 16.486842105263158,
+"Frames &amp; Audio": 14.618055555555555
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 6.0,
+"Counterfactual Reasoning": 2.0833333333333335,
+"Professional Knowledge Acquisition": 12.329545454545455,
+"High-Order Narrative Deconstruction": 5.238095238095238,
+"Symbolic/Metaphorical Interpretation": 17.53205128205128,
+"Narrative Turning Point Detection": 10.912698412698413,
+"Causal Reasoning": 6.341145833333333,
+"Event Sequence Ordering": 13.362068965517242,
+"Scene Transformation Detection": 10.416666666666666,
+"Entity Attribute Change Detection": 9.75,
+"Object Appearance Ordering": 15.277777777777779,
+"Individual Social Cognition": 14.083333333333332,
+"Collective Dynamics Analysis": 6.2339743589743595,
+"General Skills Acquisition": 9.515503875968992,
+"Spatial Understanding": 8.15,
+"Counterintuitive Comprehension": 8.244047619047619,
+"Fine-Grained Action Recognition": 5.0,
+"Visual Recognition": 33.88157894736842,
+"Dyadic Interaction Dynamics": 7.552083333333333,
+"Audio-Guided Visual Description": 16.75,
+"Narrative Cloze Inference": 7.938596491228071,
+"Future Event Prediction": 6.358695652173913,
+"Entity Existence Change Detection": 7.916666666666667,
+"Temporal Periodicity Detection": 15.460526315789474,
+"Repetitive Action Counting": 13.020833333333334,
+"Temporal Action Localization": 5.625,
+"Motion Trajectory Estimation": 15.416666666666666,
+"Basic Counting": 5.048076923076923,
+"Numerical Calculation": 4.758064516129032,
+"Cross-Modal Semantic Consistency": 33.333333333333336,
+"Vision-Guided Audio Description": 6.793478260869565,
+"Visual-Audio Collaborative Reasoning": 7.116228070175439,
+"Motion Properties Analysis": 20.3125
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 23.208128078817733,
+"level_2": 14.123333333333333,
+"level_3": 17.180316091954023,
+"relevance_score": 17.69649621212121,
+"relevance_linear_score": 32.33901515151515,
+"logic_score": 17.864774114774114,
+"total": 17.75384935497295
+},
+"second_head_rating": {
+"Physical World Reasoning": 9.873737373737374,
+"Video-Based Knowledge Acquisition": 21.302681992337163,
+"Complex Plot Comprehension": 19.36302681992337,
+"Temporal Reasoning": 16.25,
+"Order": 16.577777777777776,
+"Change": 11.177884615384615,
+"Social Behavior Analysis": 19.51111111111111,
+"Action &amp; Motion": 11.948529411764707,
+"Frame-Only": 16.94736842105263,
+"Frames &amp; Audio": 28.71527777777778
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 9.25,
+"Counterfactual Reasoning": 6.5476190476190474,
+"Professional Knowledge Acquisition": 21.609848484848484,
+"High-Order Narrative Deconstruction": 8.095238095238095,
+"Symbolic/Metaphorical Interpretation": 28.237179487179485,
+"Narrative Turning Point Detection": 26.686507936507933,
+"Causal Reasoning": 20.403645833333332,
+"Event Sequence Ordering": 19.396551724137932,
+"Scene Transformation Detection": 8.333333333333334,
+"Entity Attribute Change Detection": 14.75,
+"Object Appearance Ordering": 15.74074074074074,
+"Individual Social Cognition": 30.583333333333336,
+"Collective Dynamics Analysis": 11.330128205128204,
+"General Skills Acquisition": 20.988372093023255,
+"Spatial Understanding": 8.9,
+"Counterintuitive Comprehension": 13.794642857142858,
+"Fine-Grained Action Recognition": 4.583333333333333,
+"Visual Recognition": 32.401315789473685,
+"Dyadic Interaction Dynamics": 16.84027777777778,
+"Audio-Guided Visual Description": 17.25,
+"Narrative Cloze Inference": 11.578947368421053,
+"Future Event Prediction": 10.471014492753623,
+"Entity Existence Change Detection": 7.5,
+"Temporal Periodicity Detection": 13.464912280701755,
+"Repetitive Action Counting": 7.8125,
+"Temporal Action Localization": 15.0,
+"Motion Trajectory Estimation": 12.5,
+"Basic Counting": 8.653846153846153,
+"Numerical Calculation": 4.959677419354839,
+"Cross-Modal Semantic Consistency": 39.29924242424243,
+"Vision-Guided Audio Description": 21.195652173913043,
+"Visual-Audio Collaborative Reasoning": 34.68201754385965,
+"Motion Properties Analysis": 19.53125
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 13.058292282430214,
+"level_2": 8.783333333333333,
+"level_3": 7.397030651340995,
+"relevance_score": 10.653409090909092,
+"relevance_linear_score": 22.632575757575758,
+"logic_score": 6.578144078144079,
+"total": 9.264461090303787
+},
+"second_head_rating": {
+"Physical World Reasoning": 4.642255892255892,
+"Video-Based Knowledge Acquisition": 10.560344827586206,
+"Complex Plot Comprehension": 6.810344827586207,
+"Temporal Reasoning": 6.0227272727272725,
+"Order": 12.027777777777779,
+"Change": 8.29326923076923,
+"Social Behavior Analysis": 8.044444444444444,
+"Action &amp; Motion": 7.8125,
+"Frame-Only": 16.701754385964914,
+"Frames &amp; Audio": 9.853395061728396
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 4.0,
+"Counterfactual Reasoning": 3.869047619047619,
+"Professional Knowledge Acquisition": 15.653409090909092,
+"High-Order Narrative Deconstruction": 3.968253968253968,
+"Symbolic/Metaphorical Interpretation": 8.862179487179487,
+"Narrative Turning Point Detection": 10.317460317460316,
+"Causal Reasoning": 4.21875,
+"Event Sequence Ordering": 12.068965517241379,
+"Scene Transformation Detection": 12.5,
+"Entity Attribute Change Detection": 7.75,
+"Object Appearance Ordering": 13.88888888888889,
+"Individual Social Cognition": 10.083333333333334,
+"Collective Dynamics Analysis": 9.615384615384615,
+"General Skills Acquisition": 5.348837209302325,
+"Spatial Understanding": 5.55,
+"Counterintuitive Comprehension": 4.985119047619048,
+"Fine-Grained Action Recognition": 1.6666666666666667,
+"Visual Recognition": 30.855263157894736,
+"Dyadic Interaction Dynamics": 4.21875,
+"Audio-Guided Visual Description": 5.0,
+"Narrative Cloze Inference": 3.267543859649123,
+"Future Event Prediction": 8.532608695652174,
+"Entity Existence Change Detection": 5.833333333333333,
+"Temporal Periodicity Detection": 9.320175438596491,
+"Repetitive Action Counting": 9.375,
+"Temporal Action Localization": 10.625,
+"Motion Trajectory Estimation": 6.25,
+"Basic Counting": 6.490384615384615,
+"Numerical Calculation": 7.916666666666667,
+"Cross-Modal Semantic Consistency": 23.579545454545453,
+"Vision-Guided Audio Description": 5.706521739130435,
+"Visual-Audio Collaborative Reasoning": 7.609649122807018,
+"Motion Properties Analysis": 12.109375
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 19.507389162561577,
+"level_2": 13.62,
+"level_3": 13.253113026819923,
+"relevance_score": 14.772727272727273,
+"relevance_linear_score": 29.071969696969695,
+"logic_score": 15.300671550671549,
+"total": 14.9526633374948
+},
+"second_head_rating": {
+"Physical World Reasoning": 8.897306397306398,
+"Video-Based Knowledge Acquisition": 17.452107279693486,
+"Complex Plot Comprehension": 14.449233716475096,
+"Temporal Reasoning": 16.681818181818183,
+"Order": 15.583333333333334,
+"Change": 12.98076923076923,
+"Social Behavior Analysis": 12.744444444444445,
+"Action &amp; Motion": 9.466911764705882,
+"Frame-Only": 16.263157894736842,
+"Frames &amp; Audio": 22.36111111111111
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 9.25,
+"Counterfactual Reasoning": 6.25,
+"Professional Knowledge Acquisition": 22.490530303030305,
+"High-Order Narrative Deconstruction": 15.456349206349206,
+"Symbolic/Metaphorical Interpretation": 21.298076923076923,
+"Narrative Turning Point Detection": 11.805555555555557,
+"Causal Reasoning": 18.255208333333332,
+"Event Sequence Ordering": 20.905172413793103,
+"Scene Transformation Detection": 13.020833333333334,
+"Entity Attribute Change Detection": 13.75,
+"Object Appearance Ordering": 12.731481481481481,
+"Individual Social Cognition": 22.583333333333336,
+"Collective Dynamics Analysis": 8.557692307692308,
+"General Skills Acquisition": 12.296511627906977,
+"Spatial Understanding": 8.05,
+"Counterintuitive Comprehension": 11.324404761904761,
+"Fine-Grained Action Recognition": 4.583333333333333,
+"Visual Recognition": 28.55263157894737,
+"Dyadic Interaction Dynamics": 7.03125,
+"Audio-Guided Visual Description": 7.25,
+"Narrative Cloze Inference": 6.885964912280702,
+"Future Event Prediction": 14.492753623188404,
+"Entity Existence Change Detection": 11.666666666666666,
+"Temporal Periodicity Detection": 11.513157894736842,
+"Repetitive Action Counting": 4.6875,
+"Temporal Action Localization": 16.875,
+"Motion Trajectory Estimation": 7.5,
+"Basic Counting": 7.451923076923077,
+"Numerical Calculation": 8.588709677419354,
+"Cross-Modal Semantic Consistency": 33.80681818181818,
+"Vision-Guided Audio Description": 19.293478260869566,
+"Visual-Audio Collaborative Reasoning": 27.532894736842106,
+"Motion Properties Analysis": 14.84375
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 16.336206896551722,
+"level_2": 13.421666666666667,
+"level_3": 11.19492337164751,
+"relevance_score": 14.512310606060606,
+"relevance_linear_score": 28.40909090909091,
+"logic_score": 10.64102564102564,
+"total": 13.192883895131086
+},
+"second_head_rating": {
+"Physical World Reasoning": 8.4006734006734,
+"Video-Based Knowledge Acquisition": 12.025862068965518,
+"Complex Plot Comprehension": 15.991379310344827,
+"Temporal Reasoning": 11.166666666666666,
+"Order": 19.416666666666668,
+"Change": 14.0625,
+"Social Behavior Analysis": 8.355555555555554,
+"Action &amp; Motion": 8.143382352941176,
+"Frame-Only": 18.938596491228072,
+"Frames &amp; Audio": 14.047067901234568
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 9.9,
+"Counterfactual Reasoning": 5.634920634920635,
+"Professional Knowledge Acquisition": 18.494318181818183,
+"High-Order Narrative Deconstruction": 11.28968253968254,
+"Symbolic/Metaphorical Interpretation": 18.653846153846153,
+"Narrative Turning Point Detection": 19.642857142857142,
+"Causal Reasoning": 6.236979166666667,
+"Event Sequence Ordering": 26.939655172413794,
+"Scene Transformation Detection": 23.4375,
+"Entity Attribute Change Detection": 12.75,
+"Object Appearance Ordering": 16.435185185185187,
+"Individual Social Cognition": 7.083333333333334,
+"Collective Dynamics Analysis": 8.878205128205128,
+"General Skills Acquisition": 5.406976744186046,
+"Spatial Understanding": 7.4,
+"Counterintuitive Comprehension": 10.029761904761903,
+"Fine-Grained Action Recognition": 3.5833333333333335,
+"Visual Recognition": 34.80263157894737,
+"Dyadic Interaction Dynamics": 9.114583333333334,
+"Audio-Guided Visual Description": 11.25,
+"Narrative Cloze Inference": 13.508771929824562,
+"Future Event Prediction": 18.02536231884058,
+"Entity Existence Change Detection": 8.75,
+"Temporal Periodicity Detection": 12.171052631578947,
+"Repetitive Action Counting": 5.208333333333333,
+"Temporal Action Localization": 6.875,
+"Motion Trajectory Estimation": 10.833333333333334,
+"Basic Counting": 7.6923076923076925,
+"Numerical Calculation": 8.9247311827957,
+"Cross-Modal Semantic Consistency": 37.59469696969697,
+"Vision-Guided Audio Description": 5.978260869565218,
+"Visual-Audio Collaborative Reasoning": 7.1381578947368425,
+"Motion Properties Analysis": 12.890625
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 25.73481116584565,
+"level_2": 21.718333333333334,
+"level_3": 18.242337164750957,
+"relevance_score": 21.709280303030305,
+"relevance_linear_score": 37.02651515151515,
+"logic_score": 20.29151404151404,
+"total": 21.22607157719517
+},
+"second_head_rating": {
+"Physical World Reasoning": 12.756734006734007,
+"Video-Based Knowledge Acquisition": 23.170498084291186,
+"Complex Plot Comprehension": 21.087164750957854,
+"Temporal Reasoning": 23.045454545454547,
+"Order": 31.77777777777778,
+"Change": 19.591346153846153,
+"Social Behavior Analysis": 16.466666666666665,
+"Action &amp; Motion": 11.176470588235293,
+"Frame-Only": 22.596491228070175,
+"Frames &amp; Audio": 28.49537037037037
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 12.9,
+"Counterfactual Reasoning": 12.202380952380953,
+"Professional Knowledge Acquisition": 22.821969696969695,
+"High-Order Narrative Deconstruction": 16.0515873015873,
+"Symbolic/Metaphorical Interpretation": 20.28846153846154,
+"Narrative Turning Point Detection": 26.388888888888886,
+"Causal Reasoning": 28.059895833333332,
+"Event Sequence Ordering": 44.827586206896555,
+"Scene Transformation Detection": 21.354166666666668,
+"Entity Attribute Change Detection": 23.0,
+"Object Appearance Ordering": 30.555555555555557,
+"Individual Social Cognition": 25.583333333333336,
+"Collective Dynamics Analysis": 14.326923076923077,
+"General Skills Acquisition": 23.527131782945734,
+"Spatial Understanding": 7.15,
+"Counterintuitive Comprehension": 18.050595238095237,
+"Fine-Grained Action Recognition": 4.416666666666667,
+"Visual Recognition": 37.86184210526316,
+"Dyadic Interaction Dynamics": 9.288194444444445,
+"Audio-Guided Visual Description": 14.75,
+"Narrative Cloze Inference": 21.885964912280702,
+"Future Event Prediction": 16.068840579710145,
+"Entity Existence Change Detection": 12.5,
+"Temporal Periodicity Detection": 13.596491228070175,
+"Repetitive Action Counting": 6.770833333333333,
+"Temporal Action Localization": 14.375,
+"Motion Trajectory Estimation": 13.333333333333334,
+"Basic Counting": 14.423076923076923,
+"Numerical Calculation": 10.739247311827958,
+"Cross-Modal Semantic Consistency": 33.901515151515156,
+"Vision-Guided Audio Description": 27.445652173913043,
+"Visual-Audio Collaborative Reasoning": 35.04385964912281,
+"Motion Properties Analysis": 16.796875
+}
+}</t>
+  </si>
+  <si>
+    <t>28..57</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 15.868226600985222,
+"level_2": 13.001666666666667,
+"level_3": 9.465996168582375,
+"relevance_score": 13.671875,
+"relevance_linear_score": 26.94128787878788,
+"logic_score": 9.32997557997558,
+"total": 12.192051602163962
+},
+"second_head_rating": {
+"Physical World Reasoning": 9.086700336700337,
+"Video-Based Knowledge Acquisition": 12.801724137931034,
+"Complex Plot Comprehension": 8.773946360153257,
+"Temporal Reasoning": 7.848484848484849,
+"Order": 18.833333333333332,
+"Change": 14.182692307692308,
+"Social Behavior Analysis": 6.9,
+"Action &amp; Motion": 9.834558823529411,
+"Frame-Only": 17.710526315789473,
+"Frames &amp; Audio": 14.247685185185185
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 11.25,
+"Counterfactual Reasoning": 9.523809523809524,
+"Professional Knowledge Acquisition": 17.575757575757578,
+"High-Order Narrative Deconstruction": 7.420634920634921,
+"Symbolic/Metaphorical Interpretation": 11.842948717948719,
+"Narrative Turning Point Detection": 10.714285714285714,
+"Causal Reasoning": 5.989583333333333,
+"Event Sequence Ordering": 20.474137931034484,
+"Scene Transformation Detection": 22.395833333333332,
+"Entity Attribute Change Detection": 15.0,
+"Object Appearance Ordering": 17.59259259259259,
+"Individual Social Cognition": 9.483333333333334,
+"Collective Dynamics Analysis": 4.711538461538462,
+"General Skills Acquisition": 7.916666666666667,
+"Spatial Understanding": 5.15,
+"Counterintuitive Comprehension": 10.342261904761903,
+"Fine-Grained Action Recognition": 3.3333333333333335,
+"Visual Recognition": 32.99342105263158,
+"Dyadic Interaction Dynamics": 6.579861111111111,
+"Audio-Guided Visual Description": 10.0,
+"Narrative Cloze Inference": 3.9254385964912277,
+"Future Event Prediction": 10.434782608695652,
+"Entity Existence Change Detection": 6.25,
+"Temporal Periodicity Detection": 18.092105263157894,
+"Repetitive Action Counting": 2.6041666666666665,
+"Temporal Action Localization": 18.125,
+"Motion Trajectory Estimation": 8.75,
+"Basic Counting": 10.096153846153847,
+"Numerical Calculation": 5.362903225806452,
+"Cross-Modal Semantic Consistency": 40.71969696969697,
+"Vision-Guided Audio Description": 4.891304347826087,
+"Visual-Audio Collaborative Reasoning": 7.379385964912281,
+"Motion Properties Analysis": 17.1875
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 27.058702791461414,
+"level_2": 18.885,
+"level_3": 17.016283524904214,
+"relevance_score": 20.916193181818183,
+"relevance_linear_score": 36.12689393939394,
+"logic_score": 18.652319902319903,
+"total": 20.14461090303787
+},
+"second_head_rating": {
+"Physical World Reasoning": 12.57996632996633,
+"Video-Based Knowledge Acquisition": 22.840038314176244,
+"Complex Plot Comprehension": 16.28831417624521,
+"Temporal Reasoning": 18.34090909090909,
+"Order": 25.0,
+"Change": 19.23076923076923,
+"Social Behavior Analysis": 16.96111111111111,
+"Action &amp; Motion": 12.316176470588236,
+"Frame-Only": 23.692982456140353,
+"Frames &amp; Audio": 30.01929012345679
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 13.65,
+"Counterfactual Reasoning": 10.416666666666666,
+"Professional Knowledge Acquisition": 24.782196969696972,
+"High-Order Narrative Deconstruction": 8.988095238095237,
+"Symbolic/Metaphorical Interpretation": 18.798076923076923,
+"Narrative Turning Point Detection": 20.833333333333332,
+"Causal Reasoning": 21.106770833333332,
+"Event Sequence Ordering": 29.310344827586206,
+"Scene Transformation Detection": 22.395833333333332,
+"Entity Attribute Change Detection": 25.0,
+"Object Appearance Ordering": 28.00925925925926,
+"Individual Social Cognition": 23.583333333333336,
+"Collective Dynamics Analysis": 15.128205128205128,
+"General Skills Acquisition": 20.85271317829457,
+"Spatial Understanding": 6.4,
+"Counterintuitive Comprehension": 18.764880952380953,
+"Fine-Grained Action Recognition": 8.75,
+"Visual Recognition": 39.17763157894737,
+"Dyadic Interaction Dynamics": 12.048611111111112,
+"Audio-Guided Visual Description": 12.75,
+"Narrative Cloze Inference": 15.899122807017543,
+"Future Event Prediction": 14.492753623188404,
+"Entity Existence Change Detection": 7.083333333333333,
+"Temporal Periodicity Detection": 14.144736842105264,
+"Repetitive Action Counting": 3.125,
+"Temporal Action Localization": 23.125,
+"Motion Trajectory Estimation": 12.916666666666666,
+"Basic Counting": 15.384615384615385,
+"Numerical Calculation": 11.68010752688172,
+"Cross-Modal Semantic Consistency": 41.571969696969695,
+"Vision-Guided Audio Description": 23.097826086956523,
+"Visual-Audio Collaborative Reasoning": 38.88157894736842,
+"Motion Properties Analysis": 15.234375
 }
 }</t>
   </si>
@@ -3247,13 +3724,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3269,9 +3743,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3575,1337 +4046,1519 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
     </row>
     <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.4">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="4"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="11"/>
       <c r="I2" s="3"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
+        <v>64</v>
+      </c>
+      <c r="D3" s="3">
         <v>11</v>
       </c>
-      <c r="D3" s="4">
+      <c r="E3" s="3">
         <v>29.6</v>
       </c>
-      <c r="E3" s="4">
+      <c r="F3" s="3">
         <v>25.1</v>
       </c>
-      <c r="F3" s="4">
+      <c r="G3" s="3">
         <v>26.6</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="4"/>
       <c r="I3" s="3"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
+        <v>64</v>
+      </c>
+      <c r="D4" s="3">
         <v>16.5</v>
       </c>
-      <c r="D4" s="4">
+      <c r="E4" s="3">
         <v>38.6</v>
       </c>
-      <c r="E4" s="4">
+      <c r="F4" s="3">
         <v>31.2</v>
       </c>
-      <c r="F4" s="4">
+      <c r="G4" s="3">
         <v>33.700000000000003</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="4"/>
       <c r="I4" s="3"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
+        <v>64</v>
+      </c>
+      <c r="D5" s="3">
         <v>12.4</v>
       </c>
-      <c r="D5" s="4">
+      <c r="E5" s="3">
         <v>31</v>
       </c>
-      <c r="E5" s="4">
+      <c r="F5" s="3">
         <v>27.6</v>
       </c>
-      <c r="F5" s="4">
+      <c r="G5" s="3">
         <v>28.8</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="4"/>
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="3">
+        <v>64</v>
+      </c>
+      <c r="D6" s="5">
         <v>17.899999999999999</v>
       </c>
-      <c r="D6" s="6">
+      <c r="E6" s="5">
         <v>41.4</v>
       </c>
-      <c r="E6" s="6">
+      <c r="F6" s="5">
         <v>32.700000000000003</v>
       </c>
-      <c r="F6" s="6">
+      <c r="G6" s="5">
         <v>35.700000000000003</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="8"/>
+      <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
+        <v>64</v>
+      </c>
+      <c r="D7" s="3">
         <v>7.7</v>
       </c>
-      <c r="D7" s="4">
+      <c r="E7" s="3">
         <v>23.8</v>
       </c>
-      <c r="E7" s="4">
+      <c r="F7" s="3">
         <v>21</v>
       </c>
-      <c r="F7" s="4">
+      <c r="G7" s="3">
         <v>22</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="H7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="4"/>
       <c r="I7" s="3"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="3">
+        <v>64</v>
+      </c>
+      <c r="D8" s="5">
         <v>16.7</v>
       </c>
-      <c r="D8" s="6">
+      <c r="E8" s="5">
         <v>38.299999999999997</v>
       </c>
-      <c r="E8" s="6">
+      <c r="F8" s="5">
         <v>29.5</v>
       </c>
-      <c r="F8" s="6">
+      <c r="G8" s="5">
         <v>32.5</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="H8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="8"/>
+      <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="3">
+        <v>64</v>
+      </c>
+      <c r="D9" s="5">
         <v>17.5</v>
       </c>
-      <c r="D9" s="6">
+      <c r="E9" s="5">
         <v>40.799999999999997</v>
       </c>
-      <c r="E9" s="6">
+      <c r="F9" s="5">
         <v>31.7</v>
       </c>
-      <c r="F9" s="6">
+      <c r="G9" s="5">
         <v>34.799999999999997</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="H9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="8"/>
+      <c r="I9" s="5"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="3">
+        <v>64</v>
+      </c>
+      <c r="D10" s="5">
         <v>17.3</v>
       </c>
-      <c r="D10" s="6">
+      <c r="E10" s="5">
         <v>40.9</v>
       </c>
-      <c r="E10" s="6">
+      <c r="F10" s="5">
         <v>31.4</v>
       </c>
-      <c r="F10" s="6">
+      <c r="G10" s="5">
         <v>34.700000000000003</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="H10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="8"/>
+      <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
+        <v>64</v>
+      </c>
+      <c r="D11" s="3">
         <v>18.3</v>
       </c>
-      <c r="D11" s="4">
+      <c r="E11" s="3">
         <v>38.4</v>
       </c>
-      <c r="E11" s="4">
+      <c r="F11" s="3">
         <v>34.9</v>
       </c>
-      <c r="F11" s="4">
+      <c r="G11" s="3">
         <v>36.1</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="4"/>
       <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
+        <v>64</v>
+      </c>
+      <c r="D12" s="3">
         <v>26.3</v>
       </c>
-      <c r="D12" s="4">
+      <c r="E12" s="3">
         <v>48.4</v>
       </c>
-      <c r="E12" s="4">
+      <c r="F12" s="3">
         <v>42.3</v>
       </c>
-      <c r="F12" s="4">
+      <c r="G12" s="3">
         <v>44.4</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H12" s="4"/>
       <c r="I12" s="3"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="3">
+        <v>64</v>
+      </c>
+      <c r="D13" s="3">
         <v>10.5</v>
       </c>
-      <c r="D13" s="4">
+      <c r="E13" s="3">
         <v>27.8</v>
       </c>
-      <c r="E13" s="4">
+      <c r="F13" s="3">
         <v>23.6</v>
       </c>
-      <c r="F13" s="4">
+      <c r="G13" s="3">
         <v>25</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="H13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="4"/>
       <c r="I13" s="3"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="3">
+        <v>64</v>
+      </c>
+      <c r="D14" s="3">
         <v>15.3</v>
       </c>
-      <c r="D14" s="4">
+      <c r="E14" s="3">
         <v>38.799999999999997</v>
       </c>
-      <c r="E14" s="4">
+      <c r="F14" s="3">
         <v>28.6</v>
       </c>
-      <c r="F14" s="4">
+      <c r="G14" s="3">
         <v>32.1</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="H14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="4"/>
       <c r="I14" s="3"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="3">
+        <v>64</v>
+      </c>
+      <c r="D15" s="3">
         <v>14</v>
       </c>
-      <c r="D15" s="4">
+      <c r="E15" s="3">
         <v>33.299999999999997</v>
       </c>
-      <c r="E15" s="4">
+      <c r="F15" s="3">
         <v>28.7</v>
       </c>
-      <c r="F15" s="4">
+      <c r="G15" s="3">
         <v>30.2</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="H15" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A16" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="3">
+        <v>64</v>
+      </c>
+      <c r="D16" s="3">
+        <v>21.8</v>
+      </c>
+      <c r="E16" s="3">
+        <v>45.5</v>
+      </c>
+      <c r="F16" s="3">
+        <v>36.1</v>
+      </c>
+      <c r="G16" s="3">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="3">
+        <v>64</v>
+      </c>
+      <c r="D17" s="3">
+        <v>9.9</v>
+      </c>
+      <c r="E17" s="3">
+        <v>27.2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>23.9</v>
+      </c>
+      <c r="G17" s="3">
+        <v>25</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="3">
+        <v>64</v>
+      </c>
+      <c r="D18" s="3">
+        <v>14.6</v>
+      </c>
+      <c r="E18" s="3">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="F18" s="3">
+        <v>29.4</v>
+      </c>
+      <c r="G18" s="3">
+        <v>31.7</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="3">
+        <v>64</v>
+      </c>
+      <c r="D19" s="3">
+        <v>11.2</v>
+      </c>
+      <c r="E19" s="3">
+        <v>30.2</v>
+      </c>
+      <c r="F19" s="3">
+        <v>24.8</v>
+      </c>
+      <c r="G19" s="3">
+        <v>26.7</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="3">
+        <v>64</v>
+      </c>
+      <c r="D20" s="3">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="E20" s="3">
+        <v>39.1</v>
+      </c>
+      <c r="F20" s="3">
+        <v>29.9</v>
+      </c>
+      <c r="G20" s="3">
+        <v>33.1</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="3">
+        <v>64</v>
+      </c>
+      <c r="D21" s="3">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3">
+        <v>23</v>
+      </c>
+      <c r="F21" s="3">
+        <v>20.6</v>
+      </c>
+      <c r="G21" s="3">
+        <v>21.4</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A22" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="3">
+        <v>64</v>
+      </c>
+      <c r="D22" s="3">
+        <v>15.5</v>
+      </c>
+      <c r="E22" s="3">
+        <v>37.4</v>
+      </c>
+      <c r="F22" s="3">
+        <v>30.5</v>
+      </c>
+      <c r="G22" s="3">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="3">
+        <v>64</v>
+      </c>
+      <c r="D23" s="3">
+        <v>15.5</v>
+      </c>
+      <c r="E23" s="3">
+        <v>37.5</v>
+      </c>
+      <c r="F23" s="3">
+        <v>31.3</v>
+      </c>
+      <c r="G23" s="3">
+        <v>33.4</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="3">
+        <v>64</v>
+      </c>
+      <c r="D24" s="3">
+        <v>21.8</v>
+      </c>
+      <c r="E24" s="3">
+        <v>47.2</v>
+      </c>
+      <c r="F24" s="3">
+        <v>37.4</v>
+      </c>
+      <c r="G24" s="3">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="4">
-        <v>21.8</v>
-      </c>
-      <c r="D16" s="4">
-        <v>45.5</v>
-      </c>
-      <c r="E16" s="4">
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="3">
+        <v>64</v>
+      </c>
+      <c r="D25" s="3">
+        <v>15.1</v>
+      </c>
+      <c r="E25" s="3">
+        <v>33.6</v>
+      </c>
+      <c r="F25" s="3">
+        <v>31</v>
+      </c>
+      <c r="G25" s="3">
+        <v>31.9</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A26" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="3">
+        <v>64</v>
+      </c>
+      <c r="D26" s="3">
+        <v>19</v>
+      </c>
+      <c r="E26" s="3">
+        <v>41.9</v>
+      </c>
+      <c r="F26" s="3">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="G26" s="3">
+        <v>37.6</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I26" s="3"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A27" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="3">
+        <v>64</v>
+      </c>
+      <c r="D27" s="3">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="E27" s="3">
+        <v>26.4</v>
+      </c>
+      <c r="F27" s="3">
+        <v>23.6</v>
+      </c>
+      <c r="G27" s="3">
+        <v>24.6</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="I27" s="3"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A28" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="3">
+        <v>64</v>
+      </c>
+      <c r="D28" s="3">
+        <v>14.3</v>
+      </c>
+      <c r="E28" s="3">
+        <v>36.5</v>
+      </c>
+      <c r="F28" s="3">
+        <v>27</v>
+      </c>
+      <c r="G28" s="3">
+        <v>30.2</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A29" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="3">
+        <v>64</v>
+      </c>
+      <c r="D29" s="3">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E29" s="3">
+        <v>26.8</v>
+      </c>
+      <c r="F29" s="3">
+        <v>24.2</v>
+      </c>
+      <c r="G29" s="3">
+        <v>25.1</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A30" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="3">
+        <v>64</v>
+      </c>
+      <c r="D30" s="3">
+        <v>13.7</v>
+      </c>
+      <c r="E30" s="3">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="F30" s="3">
+        <v>27.7</v>
+      </c>
+      <c r="G30" s="3">
+        <v>30.6</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A31" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="3">
+        <v>64</v>
+      </c>
+      <c r="D31" s="3">
+        <v>7.4</v>
+      </c>
+      <c r="E31" s="3">
+        <v>21</v>
+      </c>
+      <c r="F31" s="3">
+        <v>19.3</v>
+      </c>
+      <c r="G31" s="3">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I31" s="3"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A32" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="3">
+        <v>64</v>
+      </c>
+      <c r="D32" s="3">
+        <v>9.4</v>
+      </c>
+      <c r="E32" s="3">
+        <v>27.4</v>
+      </c>
+      <c r="F32" s="3">
+        <v>22.1</v>
+      </c>
+      <c r="G32" s="3">
+        <v>23.9</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A33" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="3">
+        <v>64</v>
+      </c>
+      <c r="D33" s="3">
+        <v>11.4</v>
+      </c>
+      <c r="E33" s="3">
+        <v>28.8</v>
+      </c>
+      <c r="F33" s="3">
+        <v>26.3</v>
+      </c>
+      <c r="G33" s="3">
+        <v>27.1</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A34" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="3">
+        <v>64</v>
+      </c>
+      <c r="D34" s="3">
+        <v>17.8</v>
+      </c>
+      <c r="E34" s="3">
+        <v>40.1</v>
+      </c>
+      <c r="F34" s="3">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="G34" s="3">
+        <v>35</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="I34" s="3"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A35" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="3">
+        <v>64</v>
+      </c>
+      <c r="D35" s="3">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="E35" s="3">
+        <v>27.4</v>
+      </c>
+      <c r="F35" s="3">
+        <v>24.3</v>
+      </c>
+      <c r="G35" s="3">
+        <v>25.3</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="3">
+        <v>64</v>
+      </c>
+      <c r="D36" s="3">
+        <v>14.6</v>
+      </c>
+      <c r="E36" s="3">
+        <v>37.4</v>
+      </c>
+      <c r="F36" s="3">
+        <v>28.7</v>
+      </c>
+      <c r="G36" s="3">
+        <v>31.7</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="I36" s="3"/>
+    </row>
+    <row r="37" spans="1:9" ht="15" x14ac:dyDescent="0.4">
+      <c r="A37" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="3"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A38" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="3">
+        <v>64</v>
+      </c>
+      <c r="D38" s="3">
+        <v>11.2</v>
+      </c>
+      <c r="E38" s="3">
+        <v>24.5</v>
+      </c>
+      <c r="F38" s="3">
+        <v>26.3</v>
+      </c>
+      <c r="G38" s="3">
+        <v>25.7</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I38" s="3"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A39" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="3">
+        <v>64</v>
+      </c>
+      <c r="D39" s="3">
+        <v>18.8</v>
+      </c>
+      <c r="E39" s="3">
+        <v>39.1</v>
+      </c>
+      <c r="F39" s="3">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="G39" s="3">
+        <v>35.6</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I39" s="3"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A40" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40" s="3">
+        <v>64</v>
+      </c>
+      <c r="D40" s="3">
+        <v>12.2</v>
+      </c>
+      <c r="E40" s="3">
+        <v>27.3</v>
+      </c>
+      <c r="F40" s="3">
+        <v>26.5</v>
+      </c>
+      <c r="G40" s="3">
+        <v>26.8</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I40" s="3"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A41" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C41" s="3">
+        <v>64</v>
+      </c>
+      <c r="D41" s="5">
+        <v>20.3</v>
+      </c>
+      <c r="E41" s="5">
+        <v>42.7</v>
+      </c>
+      <c r="F41" s="5">
+        <v>34.4</v>
+      </c>
+      <c r="G41" s="5">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="I41" s="3"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A42" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="3">
+        <v>64</v>
+      </c>
+      <c r="D42" s="3">
+        <v>12.3</v>
+      </c>
+      <c r="E42" s="3">
+        <v>29.76</v>
+      </c>
+      <c r="F42" s="3">
+        <v>27.65</v>
+      </c>
+      <c r="G42" s="3">
+        <v>28.37</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I42" s="3"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A43" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="3">
+        <v>64</v>
+      </c>
+      <c r="D43" s="3">
+        <v>18</v>
+      </c>
+      <c r="E43" s="3">
+        <v>39.1</v>
+      </c>
+      <c r="F43" s="3">
+        <v>31.1</v>
+      </c>
+      <c r="G43" s="3">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="I43" s="3"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A44" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C44" s="3">
+        <v>64</v>
+      </c>
+      <c r="D44" s="5">
+        <v>18.5</v>
+      </c>
+      <c r="E44" s="5">
+        <v>41.4</v>
+      </c>
+      <c r="F44" s="5">
+        <v>33.4</v>
+      </c>
+      <c r="G44" s="5">
         <v>36.1</v>
       </c>
-      <c r="F16" s="4">
-        <v>39.299999999999997</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A17" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="4">
-        <v>9.9</v>
-      </c>
-      <c r="D17" s="4">
-        <v>27.2</v>
-      </c>
-      <c r="E17" s="4">
-        <v>23.9</v>
-      </c>
-      <c r="F17" s="4">
-        <v>25</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H17" s="4"/>
-      <c r="I17" s="3"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="4">
-        <v>14.6</v>
-      </c>
-      <c r="D18" s="4">
-        <v>36.200000000000003</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="H44" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I44" s="5"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A45" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C45" s="3">
+        <v>64</v>
+      </c>
+      <c r="D45" s="5">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="E45" s="5">
+        <v>44.8</v>
+      </c>
+      <c r="F45" s="5">
+        <v>34.6</v>
+      </c>
+      <c r="G45" s="5">
+        <v>38.1</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I45" s="5"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A46" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C46" s="3">
+        <v>64</v>
+      </c>
+      <c r="D46" s="5">
+        <v>15.7</v>
+      </c>
+      <c r="E46" s="5">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="F46" s="5">
+        <v>31.6</v>
+      </c>
+      <c r="G46" s="5">
+        <v>33</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I46" s="3"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A47" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C47" s="3">
+        <v>64</v>
+      </c>
+      <c r="D47" s="5">
+        <v>25.8</v>
+      </c>
+      <c r="E47" s="5">
+        <v>49.9</v>
+      </c>
+      <c r="F47" s="5">
+        <v>40.6</v>
+      </c>
+      <c r="G47" s="5">
+        <v>43.8</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I47" s="3"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A48" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C48" s="3">
+        <v>64</v>
+      </c>
+      <c r="D48" s="3">
+        <v>11.9</v>
+      </c>
+      <c r="E48" s="3">
+        <v>29.9</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G48" s="3">
+        <v>27.1</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I48" s="3"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A49" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C49" s="3">
+        <v>64</v>
+      </c>
+      <c r="D49" s="3">
+        <v>15.9</v>
+      </c>
+      <c r="E49" s="3">
+        <v>37.1</v>
+      </c>
+      <c r="F49" s="3">
+        <v>30.6</v>
+      </c>
+      <c r="G49" s="3">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I49" s="3"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A50" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="3">
+        <v>64</v>
+      </c>
+      <c r="D50" s="3">
+        <v>11.7</v>
+      </c>
+      <c r="E50" s="3">
         <v>29.4</v>
       </c>
-      <c r="F18" s="4">
-        <v>31.7</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="4"/>
-      <c r="I18" s="3"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="4">
-        <v>11.2</v>
-      </c>
-      <c r="D19" s="4">
-        <v>30.2</v>
-      </c>
-      <c r="E19" s="4">
-        <v>24.8</v>
-      </c>
-      <c r="F19" s="4">
-        <v>26.7</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H19" s="4"/>
-      <c r="I19" s="3"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A20" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="4">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="D20" s="4">
-        <v>39.1</v>
-      </c>
-      <c r="E20" s="4">
+      <c r="F50" s="3">
+        <v>26.3</v>
+      </c>
+      <c r="G50" s="3">
+        <v>27.4</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I50" s="2"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A51" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51" s="3">
+        <v>64</v>
+      </c>
+      <c r="D51" s="3">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="E51" s="3">
+        <v>41.3</v>
+      </c>
+      <c r="F51" s="3">
+        <v>33</v>
+      </c>
+      <c r="G51" s="3">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I51" s="3"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A52" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C52" s="3">
+        <v>64</v>
+      </c>
+      <c r="D52" s="3">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="E52" s="3">
+        <v>24</v>
+      </c>
+      <c r="F52" s="3">
+        <v>22.6</v>
+      </c>
+      <c r="G52" s="3">
+        <v>23.1</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I52" s="3"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A53" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53" s="3">
+        <v>64</v>
+      </c>
+      <c r="D53" s="3">
+        <v>15</v>
+      </c>
+      <c r="E53" s="3">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="F53" s="3">
+        <v>29.1</v>
+      </c>
+      <c r="G53" s="3">
+        <v>31.5</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I53" s="3"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A54" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C54" s="3">
+        <v>64</v>
+      </c>
+      <c r="D54" s="3">
+        <v>13.2</v>
+      </c>
+      <c r="E54" s="3">
         <v>29.9</v>
       </c>
-      <c r="F20" s="4">
-        <v>33.1</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H20" s="4"/>
-      <c r="I20" s="3"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A21" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="4">
-        <v>8</v>
-      </c>
-      <c r="D21" s="4">
-        <v>23</v>
-      </c>
-      <c r="E21" s="4">
-        <v>20.6</v>
-      </c>
-      <c r="F21" s="4">
-        <v>21.4</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="H21" s="4"/>
-      <c r="I21" s="3"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="4">
-        <v>15.5</v>
-      </c>
-      <c r="D22" s="4">
-        <v>37.4</v>
-      </c>
-      <c r="E22" s="4">
-        <v>30.5</v>
-      </c>
-      <c r="F22" s="4">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="H22" s="4"/>
-      <c r="I22" s="3"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A23" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="4">
-        <v>15.5</v>
-      </c>
-      <c r="D23" s="4">
-        <v>37.5</v>
-      </c>
-      <c r="E23" s="4">
-        <v>31.3</v>
-      </c>
-      <c r="F23" s="4">
-        <v>33.4</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="H23" s="4"/>
-      <c r="I23" s="3"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A24" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="4">
-        <v>21.8</v>
-      </c>
-      <c r="D24" s="4">
-        <v>47.2</v>
-      </c>
-      <c r="E24" s="4">
-        <v>37.4</v>
-      </c>
-      <c r="F24" s="4">
-        <v>40.700000000000003</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="H24" s="4"/>
-      <c r="I24" s="3"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A25" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="4">
-        <v>15.1</v>
-      </c>
-      <c r="D25" s="4">
-        <v>33.6</v>
-      </c>
-      <c r="E25" s="4">
-        <v>31</v>
-      </c>
-      <c r="F25" s="4">
-        <v>31.9</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="3"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A26" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="4">
-        <v>19</v>
-      </c>
-      <c r="D26" s="4">
-        <v>41.9</v>
-      </c>
-      <c r="E26" s="4">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="F26" s="4">
-        <v>37.6</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="H26" s="4"/>
-      <c r="I26" s="3"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A27" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="4">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="D27" s="4">
-        <v>26.4</v>
-      </c>
-      <c r="E27" s="4">
-        <v>23.6</v>
-      </c>
-      <c r="F27" s="4">
-        <v>24.6</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="H27" s="4"/>
-      <c r="I27" s="3"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A28" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="4">
-        <v>14.3</v>
-      </c>
-      <c r="D28" s="4">
-        <v>36.5</v>
-      </c>
-      <c r="E28" s="4">
-        <v>27</v>
-      </c>
-      <c r="F28" s="4">
-        <v>30.2</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="H28" s="4"/>
-      <c r="I28" s="3"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B29" s="5" t="s">
+      <c r="F54" s="3">
+        <v>28.4</v>
+      </c>
+      <c r="G54" s="3">
+        <v>28.9</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="I54" s="3"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A55" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C55" s="3">
         <v>64</v>
       </c>
-      <c r="C29" s="4">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="D29" s="4">
-        <v>26.8</v>
-      </c>
-      <c r="E29" s="4">
-        <v>24.2</v>
-      </c>
-      <c r="F29" s="4">
-        <v>25.1</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="H29" s="4"/>
-      <c r="I29" s="3"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A30" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B30" s="5" t="s">
+      <c r="D55" s="3">
+        <v>21.2</v>
+      </c>
+      <c r="E55" s="3">
+        <v>44.4</v>
+      </c>
+      <c r="F55" s="3">
+        <v>37</v>
+      </c>
+      <c r="G55" s="3">
+        <v>39.5</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I55" s="3"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A56" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C56" s="3">
         <v>64</v>
       </c>
-      <c r="C30" s="4">
-        <v>13.7</v>
-      </c>
-      <c r="D30" s="4">
-        <v>36.200000000000003</v>
-      </c>
-      <c r="E30" s="4">
-        <v>27.7</v>
-      </c>
-      <c r="F30" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="H30" s="4"/>
-      <c r="I30" s="3"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A31" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C31" s="4">
-        <v>7.4</v>
-      </c>
-      <c r="D31" s="4">
-        <v>21</v>
-      </c>
-      <c r="E31" s="4">
-        <v>19.3</v>
-      </c>
-      <c r="F31" s="4">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="H31" s="4"/>
-      <c r="I31" s="3"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A32" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="4">
-        <v>9.4</v>
-      </c>
-      <c r="D32" s="4">
-        <v>27.4</v>
-      </c>
-      <c r="E32" s="4">
-        <v>22.1</v>
-      </c>
-      <c r="F32" s="4">
-        <v>23.9</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H32" s="4"/>
-      <c r="I32" s="3"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A33" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A34" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A35" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C35" s="4">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="D35" s="4">
-        <v>27.4</v>
-      </c>
-      <c r="E35" s="4">
-        <v>24.3</v>
-      </c>
-      <c r="F35" s="4">
-        <v>25.3</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A36" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="4">
-        <v>14.6</v>
-      </c>
-      <c r="D36" s="4">
-        <v>37.4</v>
-      </c>
-      <c r="E36" s="4">
-        <v>28.7</v>
-      </c>
-      <c r="F36" s="4">
-        <v>31.7</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="H36" s="4"/>
-      <c r="I36" s="3"/>
-    </row>
-    <row r="37" spans="1:9" ht="15" x14ac:dyDescent="0.4">
-      <c r="A37" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A38" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" s="4">
-        <v>11.2</v>
-      </c>
-      <c r="D38" s="4">
-        <v>24.5</v>
-      </c>
-      <c r="E38" s="4">
-        <v>26.3</v>
-      </c>
-      <c r="F38" s="4">
-        <v>25.7</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A39" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" s="4">
-        <v>18.8</v>
-      </c>
-      <c r="D39" s="4">
-        <v>39.1</v>
-      </c>
-      <c r="E39" s="4">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="F39" s="4">
-        <v>35.6</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A40" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C40" s="4">
+      <c r="D56" s="3">
         <v>12.2</v>
       </c>
-      <c r="D40" s="4">
-        <v>27.3</v>
-      </c>
-      <c r="E40" s="4">
-        <v>26.5</v>
-      </c>
-      <c r="F40" s="4">
-        <v>26.8</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A41" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C41" s="6">
-        <v>20.3</v>
-      </c>
-      <c r="D41" s="6">
-        <v>42.7</v>
-      </c>
-      <c r="E41" s="6">
-        <v>34.4</v>
-      </c>
-      <c r="F41" s="6">
-        <v>37.200000000000003</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="H41" s="4"/>
-      <c r="I41" s="6"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A42" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C42" s="4">
-        <v>12.3</v>
-      </c>
-      <c r="D42" s="4">
-        <v>29.76</v>
-      </c>
-      <c r="E42" s="4">
-        <v>27.65</v>
-      </c>
-      <c r="F42" s="4">
-        <v>28.37</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A43" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C43" s="4">
-        <v>18</v>
-      </c>
-      <c r="D43" s="4">
-        <v>39.1</v>
-      </c>
-      <c r="E43" s="4">
-        <v>31.1</v>
-      </c>
-      <c r="F43" s="4">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A44" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C44" s="6">
-        <v>18.5</v>
-      </c>
-      <c r="D44" s="6">
-        <v>41.4</v>
-      </c>
-      <c r="E44" s="6">
-        <v>33.4</v>
-      </c>
-      <c r="F44" s="6">
+      <c r="E56" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F56" s="3">
+        <v>26.9</v>
+      </c>
+      <c r="G56" s="3">
+        <v>27.5</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="I56" s="3"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A57" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C57" s="3">
+        <v>64</v>
+      </c>
+      <c r="D57" s="3">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="E57" s="3">
+        <v>42.5</v>
+      </c>
+      <c r="F57" s="3">
         <v>36.1</v>
       </c>
-      <c r="G44" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A45" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C45" s="6">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="D45" s="6">
-        <v>44.8</v>
-      </c>
-      <c r="E45" s="6">
-        <v>34.6</v>
-      </c>
-      <c r="F45" s="6">
-        <v>38.1</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A46" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C46" s="6">
-        <v>15.7</v>
-      </c>
-      <c r="D46" s="6">
-        <v>35.700000000000003</v>
-      </c>
-      <c r="E46" s="6">
-        <v>31.6</v>
-      </c>
-      <c r="F46" s="6">
-        <v>33</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A47" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C47" s="6">
-        <v>25.8</v>
-      </c>
-      <c r="D47" s="6">
-        <v>49.9</v>
-      </c>
-      <c r="E47" s="6">
-        <v>40.6</v>
-      </c>
-      <c r="F47" s="6">
-        <v>43.8</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A48" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C48" s="4">
-        <v>11.9</v>
-      </c>
-      <c r="D48" s="4">
-        <v>29.9</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F48" s="4">
-        <v>27.1</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A49" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C49" s="4">
-        <v>15.9</v>
-      </c>
-      <c r="D49" s="4">
-        <v>37.1</v>
-      </c>
-      <c r="E49" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="F49" s="4">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A50" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C50" s="4">
-        <v>11.7</v>
-      </c>
-      <c r="D50" s="4">
-        <v>29.4</v>
-      </c>
-      <c r="E50" s="4">
-        <v>26.3</v>
-      </c>
-      <c r="F50" s="4">
-        <v>27.4</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="H50" s="3"/>
-      <c r="I50" s="4"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A51" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C51" s="4">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="D51" s="4">
-        <v>41.3</v>
-      </c>
-      <c r="E51" s="4">
-        <v>33</v>
-      </c>
-      <c r="F51" s="4">
-        <v>35.799999999999997</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A52" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A53" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A54" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A55" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A56" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A57" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
+      <c r="G57" s="3">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I57" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A37:H37"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/figs/exps/performance.xlsx
+++ b/figs/exps/performance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\GitHub\VideoMMEv2\figs\exps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A1ABB7-9B9C-4F32-B4FC-AEA5233B5F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9978FFD-9A10-49D3-BB6D-86816262224E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="2880" windowWidth="17280" windowHeight="10523" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="151">
   <si>
     <t>模型</t>
   </si>
@@ -2860,9 +2860,6 @@
 }</t>
   </si>
   <si>
-    <t>25/62</t>
-  </si>
-  <si>
     <t>{
 "final_rating": {
 "level_1": 17.71551724137931,
@@ -3585,6 +3582,498 @@
 "Vision-Guided Audio Description": 23.097826086956523,
 "Visual-Audio Collaborative Reasoning": 38.88157894736842,
 "Motion Properties Analysis": 15.234375
+}
+}</t>
+  </si>
+  <si>
+    <t>Qwen3-Omni-30B-A3B-Instruct-wo-audio</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 15.340722495894909,
+"level_2": 11.773333333333332,
+"level_3": 10.506465517241383,
+"relevance_score": 12.902462121212121,
+"relevance_linear_score": 26.136363636363637,
+"logic_score": 10.627289377289381,
+"total": 12.127028714107366
+},
+"second_head_rating": {
+"Physical World Reasoning": 7.138047138047138,
+"Video-Based Knowledge Acquisition": 12.964559386973178,
+"Complex Plot Comprehension": 13.381226053639848,
+"Temporal Reasoning": 9.424242424242426,
+"Order": 14.5,
+"Change": 11.778846153846153,
+"Social Behavior Analysis": 8.766666666666667,
+"Action &amp; Motion": 10.661764705882353,
+"Frame-Only": 18.978070175438592,
+"Frames &amp; Audio": 12.141203703703706
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 8.15,
+"Counterfactual Reasoning": 6.25,
+"Professional Knowledge Acquisition": 14.933712121212123,
+"High-Order Narrative Deconstruction": 15.654761904761905,
+"Symbolic/Metaphorical Interpretation": 15.432692307692308,
+"Narrative Turning Point Detection": 12.797619047619047,
+"Causal Reasoning": 8.424479166666668,
+"Event Sequence Ordering": 15.301724137931034,
+"Scene Transformation Detection": 11.979166666666666,
+"Entity Attribute Change Detection": 11.25,
+"Object Appearance Ordering": 17.36111111111111,
+"Individual Social Cognition": 10.583333333333336,
+"Collective Dynamics Analysis": 7.115384615384615,
+"General Skills Acquisition": 10.949612403100774,
+"Spatial Understanding": 4.4,
+"Counterintuitive Comprehension": 9.345238095238093,
+"Fine-Grained Action Recognition": 2.9166666666666665,
+"Visual Recognition": 38.19078947368421,
+"Dyadic Interaction Dynamics": 8.663194444444445,
+"Audio-Guided Visual Description": 9.75,
+"Narrative Cloze Inference": 8.706140350877194,
+"Future Event Prediction": 10.815217391304348,
+"Entity Existence Change Detection": 12.5,
+"Temporal Periodicity Detection": 9.210526315789474,
+"Repetitive Action Counting": 7.291666666666667,
+"Temporal Action Localization": 5.625,
+"Motion Trajectory Estimation": 8.75,
+"Basic Counting": 7.211538461538462,
+"Numerical Calculation": 5.295698924731182,
+"Cross-Modal Semantic Consistency": 19.6969696969697,
+"Vision-Guided Audio Description": 7.336956521739131,
+"Visual-Audio Collaborative Reasoning": 12.24780701754386,
+"Motion Properties Analysis": 25.390625
+}
+}</t>
+  </si>
+  <si>
+    <t>Qwen3-Omni-30B-A3B-Instruct-sub-wo-audio</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 23.06239737274221,
+"level_2": 16.819999999999997,
+"level_3": 15.719588122605362,
+"relevance_score": 17.424242424242426,
+"relevance_linear_score": 32.67045454545455,
+"logic_score": 18.890415140415147,
+"total": 17.923949230129008
+},
+"second_head_rating": {
+"Physical World Reasoning": 10.1010101010101,
+"Video-Based Knowledge Acquisition": 19.889846743295013,
+"Complex Plot Comprehension": 18.165708812260533,
+"Temporal Reasoning": 17.098484848484848,
+"Order": 23.027777777777775,
+"Change": 15.024038461538462,
+"Social Behavior Analysis": 15.461111111111114,
+"Action &amp; Motion": 11.121323529411764,
+"Frame-Only": 18.802631578947366,
+"Frames &amp; Audio": 26.809413580246908
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 12.983333333333333,
+"Counterfactual Reasoning": 6.5476190476190474,
+"Professional Knowledge Acquisition": 20.24621212121212,
+"High-Order Narrative Deconstruction": 15.654761904761905,
+"Symbolic/Metaphorical Interpretation": 15.256410256410257,
+"Narrative Turning Point Detection": 25.49603174603175,
+"Causal Reasoning": 19.479166666666664,
+"Event Sequence Ordering": 34.05172413793103,
+"Scene Transformation Detection": 16.666666666666668,
+"Entity Attribute Change Detection": 17.0,
+"Object Appearance Ordering": 19.675925925925927,
+"Individual Social Cognition": 21.333333333333336,
+"Collective Dynamics Analysis": 12.724358974358974,
+"General Skills Acquisition": 19.525193798449617,
+"Spatial Understanding": 5.9,
+"Counterintuitive Comprehension": 13.943452380952381,
+"Fine-Grained Action Recognition": 2.9166666666666665,
+"Visual Recognition": 36.546052631578945,
+"Dyadic Interaction Dynamics": 12.309027777777779,
+"Audio-Guided Visual Description": 13.25,
+"Narrative Cloze Inference": 16.820175438596493,
+"Future Event Prediction": 13.786231884057973,
+"Entity Existence Change Detection": 10.416666666666666,
+"Temporal Periodicity Detection": 10.964912280701755,
+"Repetitive Action Counting": 8.854166666666666,
+"Temporal Action Localization": 10.625,
+"Motion Trajectory Estimation": 11.666666666666666,
+"Basic Counting": 6.971153846153846,
+"Numerical Calculation": 6.975806451612903,
+"Cross-Modal Semantic Consistency": 23.10606060606061,
+"Vision-Guided Audio Description": 26.358695652173914,
+"Visual-Audio Collaborative Reasoning": 38.146929824561404,
+"Motion Properties Analysis": 20.3125
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 23.702791461412154,
+"level_2": 22.865,
+"level_3": 15.895593869731801,
+"relevance_score": 21.673768939393938,
+"relevance_linear_score": 37.07386363636363,
+"logic_score": 16.907814407814406,
+"total": 20.049417394923015
+},
+"second_head_rating": {
+"Physical World Reasoning": 10.412457912457912,
+"Video-Based Knowledge Acquisition": 20.416666666666668,
+"Complex Plot Comprehension": 20.07183908045977,
+"Temporal Reasoning": 20.636363636363637,
+"Order": 28.833333333333332,
+"Change": 28.365384615384617,
+"Social Behavior Analysis": 13.044444444444444,
+"Action &amp; Motion": 13.878676470588236,
+"Frame-Only": 22.14912280701754,
+"Frames &amp; Audio": 25.069444444444443
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 7.05,
+"Counterfactual Reasoning": 8.630952380952381,
+"Professional Knowledge Acquisition": 21.571969696969695,
+"High-Order Narrative Deconstruction": 13.373015873015872,
+"Symbolic/Metaphorical Interpretation": 25.064102564102562,
+"Narrative Turning Point Detection": 24.00793650793651,
+"Causal Reasoning": 18.763020833333332,
+"Event Sequence Ordering": 33.83620689655172,
+"Scene Transformation Detection": 41.145833333333336,
+"Entity Attribute Change Detection": 30.75,
+"Object Appearance Ordering": 28.703703703703702,
+"Individual Social Cognition": 15.083333333333332,
+"Collective Dynamics Analysis": 11.682692307692308,
+"General Skills Acquisition": 19.234496124031008,
+"Spatial Understanding": 10.55,
+"Counterintuitive Comprehension": 14.62797619047619,
+"Fine-Grained Action Recognition": 7.083333333333333,
+"Visual Recognition": 38.651315789473685,
+"Dyadic Interaction Dynamics": 12.395833333333334,
+"Audio-Guided Visual Description": 30.0,
+"Narrative Cloze Inference": 16.293859649122805,
+"Future Event Prediction": 23.242753623188406,
+"Entity Existence Change Detection": 14.166666666666666,
+"Temporal Periodicity Detection": 21.38157894736842,
+"Repetitive Action Counting": 8.333333333333334,
+"Temporal Action Localization": 20.625,
+"Motion Trajectory Estimation": 13.75,
+"Basic Counting": 12.01923076923077,
+"Numerical Calculation": 10.416666666666668,
+"Cross-Modal Semantic Consistency": 37.59469696969697,
+"Vision-Guided Audio Description": 8.695652173913043,
+"Visual-Audio Collaborative Reasoning": 24.48464912280702,
+"Motion Properties Analysis": 20.3125
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 33.70894909688013,
+"level_2": 29.565,
+"level_3": 22.282088122605366,
+"relevance_score": 28.042140151515152,
+"relevance_linear_score": 43.32386363636363,
+"logic_score": 26.307997557997556,
+"total": 27.451102788181437
+},
+"second_head_rating": {
+"Physical World Reasoning": 15.669191919191919,
+"Video-Based Knowledge Acquisition": 27.064176245210728,
+"Complex Plot Comprehension": 24.659961685823752,
+"Temporal Reasoning": 34.15909090909091,
+"Order": 36.25,
+"Change": 32.57211538461539,
+"Social Behavior Analysis": 22.705555555555556,
+"Action &amp; Motion": 16.176470588235293,
+"Frame-Only": 23.81578947368421,
+"Frames &amp; Audio": 42.411265432098766
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 14.15,
+"Counterfactual Reasoning": 19.444444444444443,
+"Professional Knowledge Acquisition": 27.263257575757574,
+"High-Order Narrative Deconstruction": 12.182539682539684,
+"Symbolic/Metaphorical Interpretation": 30.881410256410255,
+"Narrative Turning Point Detection": 30.555555555555554,
+"Causal Reasoning": 36.067708333333336,
+"Event Sequence Ordering": 45.258620689655174,
+"Scene Transformation Detection": 41.666666666666664,
+"Entity Attribute Change Detection": 38.0,
+"Object Appearance Ordering": 33.56481481481482,
+"Individual Social Cognition": 29.833333333333336,
+"Collective Dynamics Analysis": 19.935897435897438,
+"General Skills Acquisition": 26.86046511627907,
+"Spatial Understanding": 7.3,
+"Counterintuitive Comprehension": 21.666666666666664,
+"Fine-Grained Action Recognition": 12.5,
+"Visual Recognition": 39.80263157894737,
+"Dyadic Interaction Dynamics": 18.28125,
+"Audio-Guided Visual Description": 36.25,
+"Narrative Cloze Inference": 23.42105263157895,
+"Future Event Prediction": 31.5036231884058,
+"Entity Existence Change Detection": 16.25,
+"Temporal Periodicity Detection": 26.31578947368421,
+"Repetitive Action Counting": 7.8125,
+"Temporal Action Localization": 25.0,
+"Motion Trajectory Estimation": 15.0,
+"Basic Counting": 18.509615384615383,
+"Numerical Calculation": 8.669354838709678,
+"Cross-Modal Semantic Consistency": 35.321969696969695,
+"Vision-Guided Audio Description": 40.21739130434783,
+"Visual-Audio Collaborative Reasoning": 51.896929824561404,
+"Motion Properties Analysis": 21.484375
+}
+}</t>
+  </si>
+  <si>
+    <t>Qwen3-Omni-30B-A3B-Think-wo_audio</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 15.30582922824302,
+"level_2": 10.446666666666667,
+"level_3": 10.137691570881229,
+"relevance_score": 13.044507575757576,
+"relevance_linear_score": 26.231060606060606,
+"logic_score": 8.641636141636141,
+"total": 11.543903454015814
+},
+"second_head_rating": {
+"Physical World Reasoning": 6.148989898989899,
+"Video-Based Knowledge Acquisition": 14.090038314176244,
+"Complex Plot Comprehension": 11.163793103448278,
+"Temporal Reasoning": 8.893939393939394,
+"Order": 12.8,
+"Change": 9.85576923076923,
+"Social Behavior Analysis": 9.627777777777776,
+"Action &amp; Motion": 9.558823529411764,
+"Frame-Only": 16.37719298245614,
+"Frames &amp; Audio": 14.363425925925927
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 4.65,
+"Counterfactual Reasoning": 5.9523809523809526,
+"Professional Knowledge Acquisition": 18.09659090909091,
+"High-Order Narrative Deconstruction": 6.428571428571429,
+"Symbolic/Metaphorical Interpretation": 17.435897435897434,
+"Narrative Turning Point Detection": 11.607142857142858,
+"Causal Reasoning": 7.330729166666667,
+"Event Sequence Ordering": 9.051724137931034,
+"Scene Transformation Detection": 16.666666666666668,
+"Entity Attribute Change Detection": 7.25,
+"Object Appearance Ordering": 16.666666666666668,
+"Individual Social Cognition": 14.083333333333336,
+"Collective Dynamics Analysis": 6.650641025641026,
+"General Skills Acquisition": 9.99031007751938,
+"Spatial Understanding": 8.9,
+"Counterintuitive Comprehension": 5.178571428571429,
+"Fine-Grained Action Recognition": 6.25,
+"Visual Recognition": 31.67763157894737,
+"Dyadic Interaction Dynamics": 8.211805555555555,
+"Audio-Guided Visual Description": 19.25,
+"Narrative Cloze Inference": 7.324561403508773,
+"Future Event Prediction": 11.068840579710145,
+"Entity Existence Change Detection": 8.75,
+"Temporal Periodicity Detection": 13.026315789473685,
+"Repetitive Action Counting": 5.729166666666667,
+"Temporal Action Localization": 14.375,
+"Motion Trajectory Estimation": 5.833333333333333,
+"Basic Counting": 8.653846153846153,
+"Numerical Calculation": 4.099462365591398,
+"Cross-Modal Semantic Consistency": 28.40909090909091,
+"Vision-Guided Audio Description": 6.25,
+"Visual-Audio Collaborative Reasoning": 7.927631578947368,
+"Motion Properties Analysis": 16.015625
+}
+}</t>
+  </si>
+  <si>
+    <t>Qwen3-Omni-30B-A3B-Think-sub-wo_audio</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 23.73563218390806,
+"level_2": 15.135000000000002,
+"level_3": 16.13266283524904,
+"relevance_score": 16.938920454545453,
+"relevance_linear_score": 31.297348484848484,
+"logic_score": 19.313186813186817,
+"total": 17.74812734082397
+},
+"second_head_rating": {
+"Physical World Reasoning": 9.86952861952862,
+"Video-Based Knowledge Acquisition": 24.3007662835249,
+"Complex Plot Comprehension": 16.580459770114945,
+"Temporal Reasoning": 17.81818181818182,
+"Order": 18.383333333333333,
+"Change": 11.298076923076923,
+"Social Behavior Analysis": 14.405555555555553,
+"Action &amp; Motion": 12.316176470588236,
+"Frame-Only": 19.285087719298243,
+"Frames &amp; Audio": 27.65046296296296
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 13.4,
+"Counterfactual Reasoning": 8.928571428571429,
+"Professional Knowledge Acquisition": 29.952651515151505,
+"High-Order Narrative Deconstruction": 10.297619047619047,
+"Symbolic/Metaphorical Interpretation": 18.89423076923077,
+"Narrative Turning Point Detection": 20.13888888888889,
+"Causal Reasoning": 20.755208333333336,
+"Event Sequence Ordering": 24.78448275862069,
+"Scene Transformation Detection": 13.541666666666666,
+"Entity Attribute Change Detection": 11.25,
+"Object Appearance Ordering": 18.51851851851852,
+"Individual Social Cognition": 22.08333333333333,
+"Collective Dynamics Analysis": 11.442307692307692,
+"General Skills Acquisition": 18.517441860465116,
+"Spatial Understanding": 3.9,
+"Counterintuitive Comprehension": 12.75297619047619,
+"Fine-Grained Action Recognition": 3.3333333333333335,
+"Visual Recognition": 35.23026315789474,
+"Dyadic Interaction Dynamics": 9.618055555555555,
+"Audio-Guided Visual Description": 17.25,
+"Narrative Cloze Inference": 16.42543859649123,
+"Future Event Prediction": 13.731884057971016,
+"Entity Existence Change Detection": 9.583333333333334,
+"Temporal Periodicity Detection": 8.421052631578947,
+"Repetitive Action Counting": 6.25,
+"Temporal Action Localization": 10.0,
+"Motion Trajectory Estimation": 13.75,
+"Basic Counting": 10.096153846153847,
+"Numerical Calculation": 7.446236559139785,
+"Cross-Modal Semantic Consistency": 25.662878787878785,
+"Vision-Guided Audio Description": 21.73913043478261,
+"Visual-Audio Collaborative Reasoning": 39.221491228070185,
+"Motion Properties Analysis": 25.390625
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 21.75287356321839,
+"level_2": 23.07166666666667,
+"level_3": 14.780890804597702,
+"relevance_score": 20.395359848484848,
+"relevance_linear_score": 35.27462121212121,
+"logic_score": 16.69871794871795,
+"total": 19.135455680399502
+},
+"second_head_rating": {
+"Physical World Reasoning": 9.688552188552189,
+"Video-Based Knowledge Acquisition": 20.603448275862068,
+"Complex Plot Comprehension": 16.68103448275862,
+"Temporal Reasoning": 14.606060606060607,
+"Order": 35.861111111111114,
+"Change": 29.807692307692307,
+"Social Behavior Analysis": 12.544444444444444,
+"Action &amp; Motion": 10.661764705882353,
+"Frame-Only": 23.68421052631579,
+"Frames &amp; Audio": 20.054012345679013
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 12.75,
+"Counterfactual Reasoning": 11.904761904761905,
+"Professional Knowledge Acquisition": 25.01893939393939,
+"High-Order Narrative Deconstruction": 10.09920634920635,
+"Symbolic/Metaphorical Interpretation": 19.34294871794872,
+"Narrative Turning Point Detection": 24.305555555555557,
+"Causal Reasoning": 17.2265625,
+"Event Sequence Ordering": 42.456896551724135,
+"Scene Transformation Detection": 47.395833333333336,
+"Entity Attribute Change Detection": 25.0,
+"Object Appearance Ordering": 36.111111111111114,
+"Individual Social Cognition": 13.833333333333332,
+"Collective Dynamics Analysis": 12.884615384615385,
+"General Skills Acquisition": 16.085271317829456,
+"Spatial Understanding": 7.4,
+"Counterintuitive Comprehension": 7.336309523809525,
+"Fine-Grained Action Recognition": 4.583333333333333,
+"Visual Recognition": 41.11842105263158,
+"Dyadic Interaction Dynamics": 10.833333333333334,
+"Audio-Guided Visual Description": 21.75,
+"Narrative Cloze Inference": 11.885964912280702,
+"Future Event Prediction": 10.960144927536232,
+"Entity Existence Change Detection": 23.75,
+"Temporal Periodicity Detection": 25.43859649122807,
+"Repetitive Action Counting": 3.6458333333333335,
+"Temporal Action Localization": 11.875,
+"Motion Trajectory Estimation": 16.25,
+"Basic Counting": 9.615384615384615,
+"Numerical Calculation": 14.112903225806452,
+"Cross-Modal Semantic Consistency": 33.333333333333336,
+"Vision-Guided Audio Description": 8.695652173913043,
+"Visual-Audio Collaborative Reasoning": 18.125,
+"Motion Properties Analysis": 15.625
+}
+}</t>
+  </si>
+  <si>
+    <t>{
+"final_rating": {
+"level_1": 30.802545155993432,
+"level_2": 29.42666666666667,
+"level_3": 23.01963601532567,
+"relevance_score": 27.23721590909091,
+"relevance_linear_score": 42.66098484848485,
+"logic_score": 26.517094017094017,
+"total": 26.99178110694965
+},
+"second_head_rating": {
+"Physical World Reasoning": 14.8989898989899,
+"Video-Based Knowledge Acquisition": 34.51149425287356,
+"Complex Plot Comprehension": 23.04597701149425,
+"Temporal Reasoning": 29.174242424242422,
+"Order": 43.02777777777778,
+"Change": 30.408653846153847,
+"Social Behavior Analysis": 20.377777777777776,
+"Action &amp; Motion": 13.878676470588236,
+"Frame-Only": 24.25,
+"Frames &amp; Audio": 36.566358024691354
+},
+"third_head_rating": {
+"Entity Persistence Tracking": 18.55,
+"Counterfactual Reasoning": 16.071428571428573,
+"Professional Knowledge Acquisition": 33.598484848484844,
+"High-Order Narrative Deconstruction": 16.845238095238095,
+"Symbolic/Metaphorical Interpretation": 21.169871794871792,
+"Narrative Turning Point Detection": 35.019841269841265,
+"Causal Reasoning": 34.296875,
+"Event Sequence Ordering": 43.31896551724138,
+"Scene Transformation Detection": 43.75,
+"Entity Attribute Change Detection": 27.75,
+"Object Appearance Ordering": 48.148148148148145,
+"Individual Social Cognition": 26.083333333333336,
+"Collective Dynamics Analysis": 17.21153846153846,
+"General Skills Acquisition": 35.44573643410853,
+"Spatial Understanding": 4.65,
+"Counterintuitive Comprehension": 19.910714285714285,
+"Fine-Grained Action Recognition": 5.0,
+"Visual Recognition": 36.51315789473684,
+"Dyadic Interaction Dynamics": 17.864583333333332,
+"Audio-Guided Visual Description": 20.75,
+"Narrative Cloze Inference": 19.232456140350877,
+"Future Event Prediction": 22.047101449275363,
+"Entity Existence Change Detection": 24.166666666666668,
+"Temporal Periodicity Detection": 35.30701754385965,
+"Repetitive Action Counting": 8.333333333333334,
+"Temporal Action Localization": 15.625,
+"Motion Trajectory Estimation": 17.916666666666668,
+"Basic Counting": 16.10576923076923,
+"Numerical Calculation": 16.048387096774192,
+"Cross-Modal Semantic Consistency": 32.196969696969695,
+"Vision-Guided Audio Description": 31.25,
+"Visual-Audio Collaborative Reasoning": 52.719298245614034,
+"Motion Properties Analysis": 21.484375
 }
 }</t>
   </si>
@@ -4039,7 +4528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:9" ht="15" x14ac:dyDescent="0.4">
@@ -4050,7 +4539,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -4275,7 +4764,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="7" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>23</v>
@@ -4284,295 +4773,295 @@
         <v>64</v>
       </c>
       <c r="D10" s="5">
-        <v>17.3</v>
+        <v>12.1</v>
       </c>
       <c r="E10" s="5">
-        <v>40.9</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="F10" s="5">
-        <v>31.4</v>
+        <v>26.1</v>
       </c>
       <c r="G10" s="5">
-        <v>34.700000000000003</v>
+        <v>28.3</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A11" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>10</v>
+      <c r="A11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="C11" s="3">
         <v>64</v>
       </c>
-      <c r="D11" s="3">
-        <v>18.3</v>
-      </c>
-      <c r="E11" s="3">
-        <v>38.4</v>
-      </c>
-      <c r="F11" s="3">
-        <v>34.9</v>
-      </c>
-      <c r="G11" s="3">
-        <v>36.1</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="3"/>
+      <c r="D11" s="5">
+        <v>17.3</v>
+      </c>
+      <c r="E11" s="5">
+        <v>40.9</v>
+      </c>
+      <c r="F11" s="5">
+        <v>31.4</v>
+      </c>
+      <c r="G11" s="5">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="5"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A12" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>10</v>
+      <c r="A12" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="C12" s="3">
         <v>64</v>
       </c>
-      <c r="D12" s="3">
-        <v>26.3</v>
-      </c>
-      <c r="E12" s="3">
-        <v>48.4</v>
-      </c>
-      <c r="F12" s="3">
-        <v>42.3</v>
-      </c>
-      <c r="G12" s="3">
-        <v>44.4</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="3"/>
+      <c r="D12" s="5">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="E12" s="5">
+        <v>42</v>
+      </c>
+      <c r="F12" s="5">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="G12" s="5">
+        <v>35.9</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C13" s="3">
         <v>64</v>
       </c>
       <c r="D13" s="3">
-        <v>10.5</v>
+        <v>18.3</v>
       </c>
       <c r="E13" s="3">
-        <v>27.8</v>
+        <v>38.4</v>
       </c>
       <c r="F13" s="3">
-        <v>23.6</v>
+        <v>34.9</v>
       </c>
       <c r="G13" s="3">
-        <v>25</v>
+        <v>36.1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I13" s="3"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C14" s="3">
-        <v>64</v>
+        <v>512</v>
       </c>
       <c r="D14" s="3">
-        <v>15.3</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="E14" s="3">
-        <v>38.799999999999997</v>
+        <v>41.9</v>
       </c>
       <c r="F14" s="3">
-        <v>28.6</v>
+        <v>37.1</v>
       </c>
       <c r="G14" s="3">
-        <v>32.1</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="I14" s="3"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C15" s="3">
         <v>64</v>
       </c>
       <c r="D15" s="3">
-        <v>14</v>
+        <v>26.3</v>
       </c>
       <c r="E15" s="3">
-        <v>33.299999999999997</v>
+        <v>48.4</v>
       </c>
       <c r="F15" s="3">
-        <v>28.7</v>
+        <v>42.3</v>
       </c>
       <c r="G15" s="3">
-        <v>30.2</v>
+        <v>44.4</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="I15" s="3"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A16" s="8" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="3">
+        <v>512</v>
+      </c>
+      <c r="D16" s="3">
+        <v>27.5</v>
+      </c>
+      <c r="E16" s="3">
+        <v>50.2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>43.3</v>
+      </c>
+      <c r="G16" s="3">
+        <v>45.7</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="C16" s="3">
-        <v>64</v>
-      </c>
-      <c r="D16" s="3">
-        <v>21.8</v>
-      </c>
-      <c r="E16" s="3">
-        <v>45.5</v>
-      </c>
-      <c r="F16" s="3">
-        <v>36.1</v>
-      </c>
-      <c r="G16" s="3">
-        <v>39.299999999999997</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>39</v>
       </c>
       <c r="C17" s="3">
         <v>64</v>
       </c>
       <c r="D17" s="3">
-        <v>9.9</v>
+        <v>10.5</v>
       </c>
       <c r="E17" s="3">
-        <v>27.2</v>
+        <v>27.8</v>
       </c>
       <c r="F17" s="3">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="G17" s="3">
         <v>25</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="I17" s="3"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" s="3" t="s">
-        <v>41</v>
+      <c r="A18" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C18" s="3">
         <v>64</v>
       </c>
       <c r="D18" s="3">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" s="3">
-        <v>36.200000000000003</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="F18" s="3">
-        <v>29.4</v>
+        <v>28.6</v>
       </c>
       <c r="G18" s="3">
-        <v>31.7</v>
+        <v>32.1</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I18" s="3"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19" s="3" t="s">
-        <v>43</v>
+      <c r="A19" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C19" s="3">
         <v>64</v>
       </c>
       <c r="D19" s="3">
-        <v>11.2</v>
+        <v>14</v>
       </c>
       <c r="E19" s="3">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="F19" s="3">
+        <v>28.7</v>
+      </c>
+      <c r="G19" s="3">
         <v>30.2</v>
       </c>
-      <c r="F19" s="3">
-        <v>24.8</v>
-      </c>
-      <c r="G19" s="3">
-        <v>26.7</v>
-      </c>
       <c r="H19" s="4" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="I19" s="3"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A20" s="3" t="s">
-        <v>45</v>
+      <c r="A20" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C20" s="3">
         <v>64</v>
       </c>
       <c r="D20" s="3">
-        <v>16.100000000000001</v>
+        <v>21.8</v>
       </c>
       <c r="E20" s="3">
-        <v>39.1</v>
+        <v>45.5</v>
       </c>
       <c r="F20" s="3">
-        <v>29.9</v>
+        <v>36.1</v>
       </c>
       <c r="G20" s="3">
-        <v>33.1</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="I20" s="3"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>39</v>
@@ -4581,25 +5070,25 @@
         <v>64</v>
       </c>
       <c r="D21" s="3">
-        <v>8</v>
+        <v>9.9</v>
       </c>
       <c r="E21" s="3">
-        <v>23</v>
+        <v>27.2</v>
       </c>
       <c r="F21" s="3">
-        <v>20.6</v>
+        <v>23.9</v>
       </c>
       <c r="G21" s="3">
-        <v>21.4</v>
+        <v>25</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="I21" s="3"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A22" s="3" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>39</v>
@@ -4608,632 +5097,632 @@
         <v>64</v>
       </c>
       <c r="D22" s="3">
-        <v>15.5</v>
+        <v>14.6</v>
       </c>
       <c r="E22" s="3">
-        <v>37.4</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="F22" s="3">
-        <v>30.5</v>
+        <v>29.4</v>
       </c>
       <c r="G22" s="3">
-        <v>32.799999999999997</v>
+        <v>31.7</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I22" s="3"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C23" s="3">
         <v>64</v>
       </c>
       <c r="D23" s="3">
-        <v>15.5</v>
+        <v>11.2</v>
       </c>
       <c r="E23" s="3">
-        <v>37.5</v>
+        <v>30.2</v>
       </c>
       <c r="F23" s="3">
-        <v>31.3</v>
+        <v>24.8</v>
       </c>
       <c r="G23" s="3">
-        <v>33.4</v>
+        <v>26.7</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="I23" s="3"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C24" s="3">
         <v>64</v>
       </c>
       <c r="D24" s="3">
-        <v>21.8</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="E24" s="3">
-        <v>47.2</v>
+        <v>39.1</v>
       </c>
       <c r="F24" s="3">
-        <v>37.4</v>
+        <v>29.9</v>
       </c>
       <c r="G24" s="3">
-        <v>40.700000000000003</v>
+        <v>33.1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="I24" s="3"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A25" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C25" s="3">
         <v>64</v>
       </c>
       <c r="D25" s="3">
-        <v>15.1</v>
+        <v>8</v>
       </c>
       <c r="E25" s="3">
-        <v>33.6</v>
+        <v>23</v>
       </c>
       <c r="F25" s="3">
-        <v>31</v>
+        <v>20.6</v>
       </c>
       <c r="G25" s="3">
-        <v>31.9</v>
+        <v>21.4</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>114</v>
+        <v>48</v>
       </c>
       <c r="I25" s="3"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C26" s="3">
         <v>64</v>
       </c>
       <c r="D26" s="3">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="E26" s="3">
-        <v>41.9</v>
+        <v>37.4</v>
       </c>
       <c r="F26" s="3">
-        <v>35.299999999999997</v>
+        <v>30.5</v>
       </c>
       <c r="G26" s="3">
-        <v>37.6</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="I26" s="3"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C27" s="3">
         <v>64</v>
       </c>
       <c r="D27" s="3">
-        <v>9.8000000000000007</v>
+        <v>15.5</v>
       </c>
       <c r="E27" s="3">
-        <v>26.4</v>
+        <v>37.5</v>
       </c>
       <c r="F27" s="3">
-        <v>23.6</v>
+        <v>31.3</v>
       </c>
       <c r="G27" s="3">
-        <v>24.6</v>
+        <v>33.4</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I27" s="3"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C28" s="3">
         <v>64</v>
       </c>
       <c r="D28" s="3">
-        <v>14.3</v>
+        <v>21.8</v>
       </c>
       <c r="E28" s="3">
-        <v>36.5</v>
+        <v>47.2</v>
       </c>
       <c r="F28" s="3">
-        <v>27</v>
+        <v>37.4</v>
       </c>
       <c r="G28" s="3">
-        <v>30.2</v>
+        <v>40.700000000000003</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I28" s="3"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C29" s="3">
         <v>64</v>
       </c>
       <c r="D29" s="3">
-        <v>10.199999999999999</v>
+        <v>15.1</v>
       </c>
       <c r="E29" s="3">
-        <v>26.8</v>
+        <v>33.6</v>
       </c>
       <c r="F29" s="3">
-        <v>24.2</v>
+        <v>31</v>
       </c>
       <c r="G29" s="3">
-        <v>25.1</v>
+        <v>31.9</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I29" s="3"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C30" s="3">
         <v>64</v>
       </c>
       <c r="D30" s="3">
-        <v>13.7</v>
+        <v>19</v>
       </c>
       <c r="E30" s="3">
-        <v>36.200000000000003</v>
+        <v>41.9</v>
       </c>
       <c r="F30" s="3">
-        <v>27.7</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="G30" s="3">
-        <v>30.6</v>
+        <v>37.6</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I30" s="3"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A31" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C31" s="3">
         <v>64</v>
       </c>
       <c r="D31" s="3">
-        <v>7.4</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="E31" s="3">
-        <v>21</v>
+        <v>26.4</v>
       </c>
       <c r="F31" s="3">
-        <v>19.3</v>
+        <v>23.6</v>
       </c>
       <c r="G31" s="3">
-        <v>19.899999999999999</v>
+        <v>24.6</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I31" s="3"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A32" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C32" s="3">
         <v>64</v>
       </c>
       <c r="D32" s="3">
-        <v>9.4</v>
+        <v>14.3</v>
       </c>
       <c r="E32" s="3">
-        <v>27.4</v>
+        <v>36.5</v>
       </c>
       <c r="F32" s="3">
-        <v>22.1</v>
+        <v>27</v>
       </c>
       <c r="G32" s="3">
-        <v>23.9</v>
+        <v>30.2</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I32" s="3"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A33" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C33" s="3">
         <v>64</v>
       </c>
       <c r="D33" s="3">
-        <v>11.4</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="E33" s="3">
-        <v>28.8</v>
+        <v>26.8</v>
       </c>
       <c r="F33" s="3">
-        <v>26.3</v>
+        <v>24.2</v>
       </c>
       <c r="G33" s="3">
-        <v>27.1</v>
+        <v>25.1</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="I33" s="3"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A34" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C34" s="3">
         <v>64</v>
       </c>
       <c r="D34" s="3">
-        <v>17.8</v>
+        <v>13.7</v>
       </c>
       <c r="E34" s="3">
-        <v>40.1</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="F34" s="3">
-        <v>32.299999999999997</v>
+        <v>27.7</v>
       </c>
       <c r="G34" s="3">
-        <v>35</v>
+        <v>30.6</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="I34" s="3"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A35" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C35" s="3">
         <v>64</v>
       </c>
       <c r="D35" s="3">
-        <v>9.8000000000000007</v>
+        <v>7.4</v>
       </c>
       <c r="E35" s="3">
-        <v>27.4</v>
+        <v>21</v>
       </c>
       <c r="F35" s="3">
-        <v>24.3</v>
+        <v>19.3</v>
       </c>
       <c r="G35" s="3">
-        <v>25.3</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I35" s="3"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A36" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C36" s="3">
         <v>64</v>
       </c>
       <c r="D36" s="3">
-        <v>14.6</v>
+        <v>9.4</v>
       </c>
       <c r="E36" s="3">
-        <v>37.4</v>
+        <v>27.4</v>
       </c>
       <c r="F36" s="3">
-        <v>28.7</v>
+        <v>22.1</v>
       </c>
       <c r="G36" s="3">
-        <v>31.7</v>
+        <v>23.9</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I36" s="3"/>
     </row>
-    <row r="37" spans="1:9" ht="15" x14ac:dyDescent="0.4">
-      <c r="A37" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="11"/>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A37" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" s="3">
+        <v>64</v>
+      </c>
+      <c r="D37" s="3">
+        <v>11.4</v>
+      </c>
+      <c r="E37" s="3">
+        <v>28.8</v>
+      </c>
+      <c r="F37" s="3">
+        <v>26.3</v>
+      </c>
+      <c r="G37" s="3">
+        <v>27.1</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>130</v>
+      </c>
       <c r="I37" s="3"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A38" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C38" s="3">
         <v>64</v>
       </c>
       <c r="D38" s="3">
-        <v>11.2</v>
+        <v>17.8</v>
       </c>
       <c r="E38" s="3">
-        <v>24.5</v>
+        <v>40.1</v>
       </c>
       <c r="F38" s="3">
-        <v>26.3</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="G38" s="3">
-        <v>25.7</v>
+        <v>35</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="I38" s="3"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A39" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C39" s="3">
         <v>64</v>
       </c>
       <c r="D39" s="3">
-        <v>18.8</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="E39" s="3">
-        <v>39.1</v>
+        <v>27.4</v>
       </c>
       <c r="F39" s="3">
-        <v>33.799999999999997</v>
+        <v>24.3</v>
       </c>
       <c r="G39" s="3">
-        <v>35.6</v>
+        <v>25.3</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="I39" s="3"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A40" s="3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C40" s="3">
         <v>64</v>
       </c>
       <c r="D40" s="3">
-        <v>12.2</v>
+        <v>14.6</v>
       </c>
       <c r="E40" s="3">
-        <v>27.3</v>
+        <v>37.4</v>
       </c>
       <c r="F40" s="3">
-        <v>26.5</v>
+        <v>28.7</v>
       </c>
       <c r="G40" s="3">
-        <v>26.8</v>
+        <v>31.7</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="I40" s="3"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A41" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C41" s="3">
-        <v>64</v>
-      </c>
-      <c r="D41" s="5">
-        <v>20.3</v>
-      </c>
-      <c r="E41" s="5">
-        <v>42.7</v>
-      </c>
-      <c r="F41" s="5">
-        <v>34.4</v>
-      </c>
-      <c r="G41" s="5">
-        <v>37.200000000000003</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>81</v>
-      </c>
+    <row r="41" spans="1:9" ht="15" x14ac:dyDescent="0.4">
+      <c r="A41" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="11"/>
       <c r="I41" s="3"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A42" s="3" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C42" s="3">
         <v>64</v>
       </c>
       <c r="D42" s="3">
-        <v>12.3</v>
+        <v>11.2</v>
       </c>
       <c r="E42" s="3">
-        <v>29.76</v>
+        <v>24.5</v>
       </c>
       <c r="F42" s="3">
-        <v>27.65</v>
+        <v>26.3</v>
       </c>
       <c r="G42" s="3">
-        <v>28.37</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>84</v>
+        <v>25.7</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="I42" s="3"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A43" s="3" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C43" s="3">
         <v>64</v>
       </c>
       <c r="D43" s="3">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="E43" s="3">
         <v>39.1</v>
       </c>
       <c r="F43" s="3">
-        <v>31.1</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="G43" s="3">
-        <v>33.799999999999997</v>
+        <v>35.6</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="I43" s="3"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A44" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>87</v>
+      <c r="A44" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="C44" s="3">
         <v>64</v>
       </c>
-      <c r="D44" s="5">
-        <v>18.5</v>
-      </c>
-      <c r="E44" s="5">
-        <v>41.4</v>
-      </c>
-      <c r="F44" s="5">
-        <v>33.4</v>
-      </c>
-      <c r="G44" s="5">
-        <v>36.1</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="I44" s="5"/>
+      <c r="D44" s="3">
+        <v>12.2</v>
+      </c>
+      <c r="E44" s="3">
+        <v>27.3</v>
+      </c>
+      <c r="F44" s="3">
+        <v>26.5</v>
+      </c>
+      <c r="G44" s="3">
+        <v>26.8</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I44" s="3"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A45" s="5" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="C45" s="3">
         <v>64</v>
       </c>
       <c r="D45" s="5">
-        <v>19.899999999999999</v>
+        <v>20.3</v>
       </c>
       <c r="E45" s="5">
-        <v>44.8</v>
+        <v>42.7</v>
       </c>
       <c r="F45" s="5">
-        <v>34.6</v>
+        <v>34.4</v>
       </c>
       <c r="G45" s="5">
-        <v>38.1</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="I45" s="5"/>
+        <v>81</v>
+      </c>
+      <c r="I45" s="3"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A46" s="3" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>83</v>
@@ -5241,26 +5730,26 @@
       <c r="C46" s="3">
         <v>64</v>
       </c>
-      <c r="D46" s="5">
-        <v>15.7</v>
-      </c>
-      <c r="E46" s="5">
-        <v>35.700000000000003</v>
-      </c>
-      <c r="F46" s="5">
-        <v>31.6</v>
-      </c>
-      <c r="G46" s="5">
-        <v>33</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>92</v>
+      <c r="D46" s="3">
+        <v>12.3</v>
+      </c>
+      <c r="E46" s="3">
+        <v>29.76</v>
+      </c>
+      <c r="F46" s="3">
+        <v>27.65</v>
+      </c>
+      <c r="G46" s="3">
+        <v>28.37</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="I46" s="3"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A47" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>83</v>
@@ -5268,297 +5757,513 @@
       <c r="C47" s="3">
         <v>64</v>
       </c>
-      <c r="D47" s="5">
-        <v>25.8</v>
-      </c>
-      <c r="E47" s="5">
-        <v>49.9</v>
-      </c>
-      <c r="F47" s="5">
-        <v>40.6</v>
-      </c>
-      <c r="G47" s="5">
-        <v>43.8</v>
+      <c r="D47" s="3">
+        <v>18</v>
+      </c>
+      <c r="E47" s="3">
+        <v>39.1</v>
+      </c>
+      <c r="F47" s="3">
+        <v>31.1</v>
+      </c>
+      <c r="G47" s="3">
+        <v>33.799999999999997</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="I47" s="3"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A48" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>96</v>
+      <c r="A48" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="C48" s="3">
         <v>64</v>
       </c>
-      <c r="D48" s="3">
-        <v>11.9</v>
-      </c>
-      <c r="E48" s="3">
-        <v>29.9</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="G48" s="3">
-        <v>27.1</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="I48" s="3"/>
+      <c r="D48" s="5">
+        <v>18.5</v>
+      </c>
+      <c r="E48" s="5">
+        <v>41.4</v>
+      </c>
+      <c r="F48" s="5">
+        <v>33.4</v>
+      </c>
+      <c r="G48" s="5">
+        <v>36.1</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I48" s="5"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A49" s="3" t="s">
-        <v>97</v>
+      <c r="A49" s="5" t="s">
+        <v>145</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="C49" s="3">
         <v>64</v>
       </c>
       <c r="D49" s="3">
-        <v>15.9</v>
+        <v>11.54</v>
       </c>
       <c r="E49" s="3">
-        <v>37.1</v>
+        <v>30.77</v>
       </c>
       <c r="F49" s="3">
-        <v>30.6</v>
+        <v>26.23</v>
       </c>
       <c r="G49" s="3">
-        <v>32.799999999999997</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>127</v>
+        <v>27.78</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="I49" s="3"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A50" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>99</v>
+      <c r="A50" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="C50" s="3">
         <v>64</v>
       </c>
-      <c r="D50" s="3">
-        <v>11.7</v>
-      </c>
-      <c r="E50" s="3">
-        <v>29.4</v>
-      </c>
-      <c r="F50" s="3">
-        <v>26.3</v>
-      </c>
-      <c r="G50" s="3">
-        <v>27.4</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="I50" s="2"/>
+      <c r="D50" s="5">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="E50" s="5">
+        <v>44.8</v>
+      </c>
+      <c r="F50" s="5">
+        <v>34.6</v>
+      </c>
+      <c r="G50" s="5">
+        <v>38.1</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I50" s="5"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A51" s="3" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="C51" s="3">
         <v>64</v>
       </c>
       <c r="D51" s="3">
-        <v>18.600000000000001</v>
+        <v>17.8</v>
       </c>
       <c r="E51" s="3">
-        <v>41.3</v>
+        <v>42.6</v>
       </c>
       <c r="F51" s="3">
-        <v>33</v>
+        <v>31.3</v>
       </c>
       <c r="G51" s="3">
-        <v>35.799999999999997</v>
+        <v>35.1</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="I51" s="3"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A52" s="3" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="C52" s="3">
         <v>64</v>
       </c>
-      <c r="D52" s="3">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="E52" s="3">
-        <v>24</v>
-      </c>
-      <c r="F52" s="3">
-        <v>22.6</v>
-      </c>
-      <c r="G52" s="3">
-        <v>23.1</v>
+      <c r="D52" s="5">
+        <v>15.7</v>
+      </c>
+      <c r="E52" s="5">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="F52" s="5">
+        <v>31.6</v>
+      </c>
+      <c r="G52" s="5">
+        <v>33</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="I52" s="3"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A53" s="3" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="C53" s="3">
-        <v>64</v>
-      </c>
-      <c r="D53" s="3">
-        <v>15</v>
-      </c>
-      <c r="E53" s="3">
-        <v>36.299999999999997</v>
-      </c>
-      <c r="F53" s="3">
-        <v>29.1</v>
-      </c>
-      <c r="G53" s="3">
-        <v>31.5</v>
+        <v>512</v>
+      </c>
+      <c r="D53" s="5">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="E53" s="5">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="F53" s="5">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="G53" s="5">
+        <v>36.799999999999997</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="I53" s="3"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A54" s="3" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="C54" s="3">
         <v>64</v>
       </c>
-      <c r="D54" s="3">
-        <v>13.2</v>
-      </c>
-      <c r="E54" s="3">
-        <v>29.9</v>
-      </c>
-      <c r="F54" s="3">
-        <v>28.4</v>
-      </c>
-      <c r="G54" s="3">
-        <v>28.9</v>
+      <c r="D54" s="5">
+        <v>25.8</v>
+      </c>
+      <c r="E54" s="5">
+        <v>49.9</v>
+      </c>
+      <c r="F54" s="5">
+        <v>40.6</v>
+      </c>
+      <c r="G54" s="5">
+        <v>43.8</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="I54" s="3"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A55" s="3" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="C55" s="3">
-        <v>64</v>
-      </c>
-      <c r="D55" s="3">
-        <v>21.2</v>
-      </c>
-      <c r="E55" s="3">
-        <v>44.4</v>
-      </c>
-      <c r="F55" s="3">
-        <v>37</v>
-      </c>
-      <c r="G55" s="3">
-        <v>39.5</v>
+        <v>512</v>
+      </c>
+      <c r="D55" s="5">
+        <v>27</v>
+      </c>
+      <c r="E55" s="5">
+        <v>50.6</v>
+      </c>
+      <c r="F55" s="5">
+        <v>42.7</v>
+      </c>
+      <c r="G55" s="5">
+        <v>45.4</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="I55" s="3"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A56" s="3" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C56" s="3">
         <v>64</v>
       </c>
       <c r="D56" s="3">
-        <v>12.2</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>137</v>
+        <v>11.9</v>
+      </c>
+      <c r="E56" s="3">
+        <v>29.9</v>
       </c>
       <c r="F56" s="3">
-        <v>26.9</v>
+        <v>25.6</v>
       </c>
       <c r="G56" s="3">
-        <v>27.5</v>
+        <v>27.1</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="I56" s="3"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A57" s="3" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C57" s="3">
         <v>64</v>
       </c>
       <c r="D57" s="3">
+        <v>15.9</v>
+      </c>
+      <c r="E57" s="3">
+        <v>37.1</v>
+      </c>
+      <c r="F57" s="3">
+        <v>30.6</v>
+      </c>
+      <c r="G57" s="3">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I57" s="3"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A58" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C58" s="3">
+        <v>64</v>
+      </c>
+      <c r="D58" s="3">
+        <v>11.7</v>
+      </c>
+      <c r="E58" s="3">
+        <v>29.4</v>
+      </c>
+      <c r="F58" s="3">
+        <v>26.3</v>
+      </c>
+      <c r="G58" s="3">
+        <v>27.4</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="I58" s="2"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A59" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C59" s="3">
+        <v>64</v>
+      </c>
+      <c r="D59" s="3">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="E59" s="3">
+        <v>41.3</v>
+      </c>
+      <c r="F59" s="3">
+        <v>33</v>
+      </c>
+      <c r="G59" s="3">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I59" s="3"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A60" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C60" s="3">
+        <v>64</v>
+      </c>
+      <c r="D60" s="3">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="E60" s="3">
+        <v>24</v>
+      </c>
+      <c r="F60" s="3">
+        <v>22.6</v>
+      </c>
+      <c r="G60" s="3">
+        <v>23.1</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="I60" s="3"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A61" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C61" s="3">
+        <v>64</v>
+      </c>
+      <c r="D61" s="3">
+        <v>15</v>
+      </c>
+      <c r="E61" s="3">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="F61" s="3">
+        <v>29.1</v>
+      </c>
+      <c r="G61" s="3">
+        <v>31.5</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I61" s="3"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A62" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C62" s="3">
+        <v>64</v>
+      </c>
+      <c r="D62" s="3">
+        <v>13.2</v>
+      </c>
+      <c r="E62" s="3">
+        <v>29.9</v>
+      </c>
+      <c r="F62" s="3">
+        <v>28.4</v>
+      </c>
+      <c r="G62" s="3">
+        <v>28.9</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I62" s="3"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A63" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C63" s="3">
+        <v>64</v>
+      </c>
+      <c r="D63" s="3">
+        <v>21.2</v>
+      </c>
+      <c r="E63" s="3">
+        <v>44.4</v>
+      </c>
+      <c r="F63" s="3">
+        <v>37</v>
+      </c>
+      <c r="G63" s="3">
+        <v>39.5</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="I63" s="3"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A64" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C64" s="3">
+        <v>64</v>
+      </c>
+      <c r="D64" s="3">
+        <v>12.2</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F64" s="3">
+        <v>26.9</v>
+      </c>
+      <c r="G64" s="3">
+        <v>27.5</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="I64" s="3"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A65" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C65" s="3">
+        <v>64</v>
+      </c>
+      <c r="D65" s="3">
         <v>20.100000000000001</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E65" s="3">
         <v>42.5</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F65" s="3">
         <v>36.1</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G65" s="3">
         <v>38.299999999999997</v>
       </c>
-      <c r="H57" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="I57" s="3"/>
+      <c r="H65" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="I65" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A41:H41"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
